--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -33,132 +33,132 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="82">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>MapType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Stage</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Dungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>StageNum</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>초원</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>MapPrefab</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BGM</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>ReqKillCount</t>
   </si>
   <si>
     <t>StageStep</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Map_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Sound_Map_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>EliteMonsterIDs</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BossMonsterID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>StepStatMultiplier</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>빙하</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>용암</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>빙하지역입니다.</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>초원지역입니다.</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>용암지역입니다.</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Map_2</t>
@@ -174,35 +174,35 @@
   </si>
   <si>
     <t>101;102;103;104;105</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>106;107;108;109;110</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>111;112;113;114;115</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>DungeonType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Gold</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Exp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>DungeonType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!DungeonType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -218,39 +218,39 @@
       </rPr>
       <t>ame</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Raid</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>TicketItemID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>TicketCost</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>UnlockCondition</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>DungeonList</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>DungeonStage</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -266,75 +266,75 @@
       </rPr>
       <t>tep</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>LimitTime</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>SpawnCount</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>StatMultiplier</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>RewardID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>NormalMonsterIDs</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>DungeonListID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>골드던전</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>경험치던전</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>레이드</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Gold</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Exp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Raid</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>경험치를 대량으로 획득 할 수 있는 던전</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>골드를 대량으로 획득 할 수 있는 던전</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>레이드 보스의 데미지를 누적하는 던전</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>퀘스트1제한</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>퀘스트2제한</t>
@@ -344,7 +344,7 @@
   </si>
   <si>
     <t>Dungeon_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Dungeon_2</t>
@@ -354,15 +354,15 @@
   </si>
   <si>
     <t>!Table</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>ClearRewardID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -379,7 +379,27 @@
       </rPr>
       <t>tageInfo</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>101;102;103</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>10001</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;10002</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -389,12 +409,20 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -576,13 +604,13 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -598,43 +626,43 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -979,7 +1007,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1231,7 +1259,7 @@
       <c r="E8" s="14"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1454,7 +1482,7 @@
       <c r="J10" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1610,10 +1638,18 @@
       <c r="E4" s="5">
         <v>120</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
+      <c r="F4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1000001</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
       <c r="J4" s="5">
         <v>0.1</v>
       </c>
@@ -1638,6 +1674,18 @@
       <c r="E5" s="5">
         <v>120</v>
       </c>
+      <c r="F5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1000001</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
       <c r="J5" s="2">
         <v>0.2</v>
       </c>
@@ -1658,6 +1706,18 @@
       <c r="E6" s="5">
         <v>120</v>
       </c>
+      <c r="F6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1000001</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
       <c r="J6" s="2">
         <v>0.3</v>
       </c>
@@ -1678,6 +1738,18 @@
       <c r="E7" s="5">
         <v>120</v>
       </c>
+      <c r="F7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1000001</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
       <c r="J7" s="2">
         <v>0.4</v>
       </c>
@@ -1698,6 +1770,18 @@
       <c r="E8" s="5">
         <v>120</v>
       </c>
+      <c r="F8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="5">
+        <v>1000001</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
       <c r="J8" s="2">
         <v>0.5</v>
       </c>
@@ -1718,6 +1802,18 @@
       <c r="E9" s="5">
         <v>120</v>
       </c>
+      <c r="F9" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1000001</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1</v>
+      </c>
       <c r="J9" s="5">
         <v>0.1</v>
       </c>
@@ -1736,6 +1832,18 @@
       <c r="E10" s="5">
         <v>120</v>
       </c>
+      <c r="F10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1000001</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1</v>
+      </c>
       <c r="J10" s="2">
         <v>0.2</v>
       </c>
@@ -1754,6 +1862,18 @@
       <c r="E11" s="5">
         <v>120</v>
       </c>
+      <c r="F11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1000001</v>
+      </c>
+      <c r="I11" s="5">
+        <v>1</v>
+      </c>
       <c r="J11" s="2">
         <v>0.3</v>
       </c>
@@ -1771,6 +1891,18 @@
       <c r="E12" s="5">
         <v>120</v>
       </c>
+      <c r="F12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1000001</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1</v>
+      </c>
       <c r="J12" s="2">
         <v>0.4</v>
       </c>
@@ -1788,6 +1920,18 @@
       <c r="E13" s="5">
         <v>120</v>
       </c>
+      <c r="F13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1000001</v>
+      </c>
+      <c r="I13" s="5">
+        <v>1</v>
+      </c>
       <c r="J13" s="2">
         <v>0.5</v>
       </c>
@@ -1805,6 +1949,18 @@
       <c r="E14" s="5">
         <v>120</v>
       </c>
+      <c r="F14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1000001</v>
+      </c>
+      <c r="I14" s="5">
+        <v>1</v>
+      </c>
       <c r="J14" s="5">
         <v>0.1</v>
       </c>
@@ -1822,6 +1978,18 @@
       <c r="E15" s="5">
         <v>120</v>
       </c>
+      <c r="F15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1000001</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
       <c r="J15" s="2">
         <v>0.2</v>
       </c>
@@ -1839,6 +2007,18 @@
       <c r="E16" s="5">
         <v>120</v>
       </c>
+      <c r="F16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1000001</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
       <c r="J16" s="2">
         <v>0.3</v>
       </c>
@@ -1856,6 +2036,18 @@
       <c r="E17" s="5">
         <v>120</v>
       </c>
+      <c r="F17" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" s="5">
+        <v>1000001</v>
+      </c>
+      <c r="I17" s="5">
+        <v>1</v>
+      </c>
       <c r="J17" s="2">
         <v>0.4</v>
       </c>
@@ -1873,12 +2065,24 @@
       <c r="E18" s="5">
         <v>120</v>
       </c>
+      <c r="F18" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18" s="5">
+        <v>1000001</v>
+      </c>
+      <c r="I18" s="5">
+        <v>1</v>
+      </c>
       <c r="J18" s="2">
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="77">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="10" type="noConversion"/>
@@ -117,10 +117,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>Map_1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>Sound_Map_1</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -159,12 +155,6 @@
   <si>
     <t>용암지역입니다.</t>
     <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map_2</t>
-  </si>
-  <si>
-    <t>Map_3</t>
   </si>
   <si>
     <t>Sound_Map_2</t>
@@ -341,16 +331,6 @@
   </si>
   <si>
     <t>퀘스트3제한</t>
-  </si>
-  <si>
-    <t>Dungeon_1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dungeon_2</t>
-  </si>
-  <si>
-    <t>Dungeon_3</t>
   </si>
   <si>
     <t>!Table</t>
@@ -400,6 +380,9 @@
       <t>;10002</t>
     </r>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab_GridMap_01</t>
   </si>
 </sst>
 </file>
@@ -940,7 +923,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -983,22 +966,22 @@
         <v>0</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -1023,7 +1006,7 @@
     <col min="4" max="4" width="10" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.375" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.75" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.25" style="2" bestFit="1" customWidth="1"/>
@@ -1039,10 +1022,10 @@
   <sheetData>
     <row r="1" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -1072,22 +1055,22 @@
         <v>18</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="15" t="s">
         <v>23</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>24</v>
       </c>
       <c r="L2" t="s">
         <v>19</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
@@ -1129,10 +1112,10 @@
         <v>12</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
@@ -1152,16 +1135,16 @@
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="I4" s="16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J4">
         <v>10001</v>
@@ -1187,19 +1170,19 @@
         <v>5</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="16" t="s">
         <v>34</v>
-      </c>
-      <c r="I5" s="16" t="s">
-        <v>37</v>
       </c>
       <c r="J5">
         <v>10002</v>
@@ -1225,19 +1208,19 @@
         <v>5</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="16" t="s">
         <v>35</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>38</v>
       </c>
       <c r="J6">
         <v>10003</v>
@@ -1278,7 +1261,7 @@
     <col min="6" max="6" width="12.375" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.25" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.125" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.5" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.5" style="2" bestFit="1" customWidth="1"/>
@@ -1302,7 +1285,7 @@
         <v>6</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
@@ -1317,22 +1300,22 @@
         <v>1</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>16</v>
@@ -1349,13 +1332,13 @@
         <v>10</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>12</v>
@@ -1364,7 +1347,7 @@
         <v>12</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I3" s="9" t="s">
         <v>17</v>
@@ -1391,22 +1374,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="G4" s="2">
         <v>1</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J4"/>
       <c r="L4" s="5"/>
@@ -1418,22 +1401,22 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="G5" s="2">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
@@ -1444,22 +1427,22 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
@@ -1520,7 +1503,7 @@
         <v>6</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
@@ -1540,31 +1523,31 @@
         <v>1</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>57</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9"/>
@@ -1586,7 +1569,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>12</v>
@@ -1601,7 +1584,7 @@
         <v>10</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>10</v>
@@ -1639,10 +1622,10 @@
         <v>120</v>
       </c>
       <c r="F4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H4" s="5">
         <v>1000001</v>
@@ -1675,10 +1658,10 @@
         <v>120</v>
       </c>
       <c r="F5" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H5" s="5">
         <v>1000001</v>
@@ -1707,10 +1690,10 @@
         <v>120</v>
       </c>
       <c r="F6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5">
         <v>1000001</v>
@@ -1739,10 +1722,10 @@
         <v>120</v>
       </c>
       <c r="F7" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H7" s="5">
         <v>1000001</v>
@@ -1771,10 +1754,10 @@
         <v>120</v>
       </c>
       <c r="F8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H8" s="5">
         <v>1000001</v>
@@ -1803,10 +1786,10 @@
         <v>120</v>
       </c>
       <c r="F9" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H9" s="5">
         <v>1000001</v>
@@ -1833,10 +1816,10 @@
         <v>120</v>
       </c>
       <c r="F10" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H10" s="5">
         <v>1000001</v>
@@ -1863,10 +1846,10 @@
         <v>120</v>
       </c>
       <c r="F11" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H11" s="5">
         <v>1000001</v>
@@ -1892,10 +1875,10 @@
         <v>120</v>
       </c>
       <c r="F12" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H12" s="5">
         <v>1000001</v>
@@ -1921,10 +1904,10 @@
         <v>120</v>
       </c>
       <c r="F13" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H13" s="5">
         <v>1000001</v>
@@ -1950,10 +1933,10 @@
         <v>120</v>
       </c>
       <c r="F14" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H14" s="5">
         <v>1000001</v>
@@ -1979,10 +1962,10 @@
         <v>120</v>
       </c>
       <c r="F15" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H15" s="5">
         <v>1000001</v>
@@ -2008,10 +1991,10 @@
         <v>120</v>
       </c>
       <c r="F16" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H16" s="5">
         <v>1000001</v>
@@ -2037,10 +2020,10 @@
         <v>120</v>
       </c>
       <c r="F17" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H17" s="5">
         <v>1000001</v>
@@ -2066,10 +2049,10 @@
         <v>120</v>
       </c>
       <c r="F18" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H18" s="5">
         <v>1000001</v>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="78">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="10" type="noConversion"/>
@@ -161,10 +161,6 @@
   </si>
   <si>
     <t>Sound_Map_3</t>
-  </si>
-  <si>
-    <t>101;102;103;104;105</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>106;107;108;109;110</t>
@@ -383,6 +379,26 @@
   </si>
   <si>
     <t>Prefab_GridMap_01</t>
+  </si>
+  <si>
+    <t>10001;10002</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>10001</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;10002</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -966,22 +982,22 @@
         <v>0</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -997,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
@@ -1009,7 +1025,7 @@
     <col min="7" max="7" width="18.875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.75" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.625" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.5" style="2" bestFit="1" customWidth="1"/>
@@ -1022,10 +1038,10 @@
   <sheetData>
     <row r="1" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -1055,7 +1071,7 @@
         <v>18</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J2" s="9" t="s">
         <v>22</v>
@@ -1070,7 +1086,7 @@
         <v>24</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
@@ -1115,7 +1131,7 @@
         <v>25</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
@@ -1138,20 +1154,15 @@
         <v>29</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4">
-        <v>10001</v>
-      </c>
-      <c r="K4" s="2">
-        <v>1000001</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="K4" s="5"/>
       <c r="L4" s="2">
         <v>100</v>
       </c>
@@ -1176,13 +1187,13 @@
         <v>28</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J5">
         <v>10002</v>
@@ -1214,13 +1225,13 @@
         <v>30</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J6">
         <v>10003</v>
@@ -1240,6 +1251,33 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E8" s="14"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I10" s="9"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I12" s="9"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I13"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I14"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I15"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I16"/>
+    </row>
+    <row r="17" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I17" s="5"/>
+    </row>
+    <row r="18" spans="9:9" x14ac:dyDescent="0.3">
+      <c r="I18" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -1285,7 +1323,7 @@
         <v>6</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
@@ -1300,22 +1338,22 @@
         <v>1</v>
       </c>
       <c r="C2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>42</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>16</v>
@@ -1332,13 +1370,13 @@
         <v>10</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>12</v>
@@ -1347,7 +1385,7 @@
         <v>12</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I3" s="9" t="s">
         <v>17</v>
@@ -1374,22 +1412,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J4"/>
       <c r="L4" s="5"/>
@@ -1401,22 +1439,22 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
@@ -1427,22 +1465,22 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
@@ -1503,7 +1541,7 @@
         <v>6</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C1" s="17"/>
       <c r="D1" s="17"/>
@@ -1523,16 +1561,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>51</v>
-      </c>
       <c r="F2" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>22</v>
@@ -1541,13 +1579,13 @@
         <v>23</v>
       </c>
       <c r="I2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>53</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>54</v>
       </c>
       <c r="L2" s="9"/>
       <c r="M2" s="9"/>
@@ -1569,7 +1607,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>12</v>
@@ -1584,7 +1622,7 @@
         <v>10</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>10</v>
@@ -1621,15 +1659,11 @@
       <c r="E4" s="5">
         <v>120</v>
       </c>
-      <c r="F4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1000001</v>
-      </c>
+      <c r="F4">
+        <v>10002</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="5"/>
       <c r="I4" s="5">
         <v>1</v>
       </c>
@@ -1658,10 +1692,10 @@
         <v>120</v>
       </c>
       <c r="F5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H5" s="5">
         <v>1000001</v>
@@ -1690,10 +1724,10 @@
         <v>120</v>
       </c>
       <c r="F6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="H6" s="5">
         <v>1000001</v>
@@ -1722,10 +1756,10 @@
         <v>120</v>
       </c>
       <c r="F7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="H7" s="5">
         <v>1000001</v>
@@ -1754,10 +1788,10 @@
         <v>120</v>
       </c>
       <c r="F8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="H8" s="5">
         <v>1000001</v>
@@ -1786,10 +1820,10 @@
         <v>120</v>
       </c>
       <c r="F9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="H9" s="5">
         <v>1000001</v>
@@ -1816,10 +1850,10 @@
         <v>120</v>
       </c>
       <c r="F10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="H10" s="5">
         <v>1000001</v>
@@ -1846,10 +1880,10 @@
         <v>120</v>
       </c>
       <c r="F11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="H11" s="5">
         <v>1000001</v>
@@ -1875,10 +1909,10 @@
         <v>120</v>
       </c>
       <c r="F12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="H12" s="5">
         <v>1000001</v>
@@ -1904,10 +1938,10 @@
         <v>120</v>
       </c>
       <c r="F13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="H13" s="5">
         <v>1000001</v>
@@ -1933,10 +1967,10 @@
         <v>120</v>
       </c>
       <c r="F14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="H14" s="5">
         <v>1000001</v>
@@ -1962,10 +1996,10 @@
         <v>120</v>
       </c>
       <c r="F15" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="H15" s="5">
         <v>1000001</v>
@@ -1991,10 +2025,10 @@
         <v>120</v>
       </c>
       <c r="F16" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="H16" s="5">
         <v>1000001</v>
@@ -2020,10 +2054,10 @@
         <v>120</v>
       </c>
       <c r="F17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="H17" s="5">
         <v>1000001</v>
@@ -2049,10 +2083,10 @@
         <v>120</v>
       </c>
       <c r="F18" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="H18" s="5">
         <v>1000001</v>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -42,184 +42,184 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>!string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>초원</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound_Map_1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>빙하</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>용암</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>빙하지역입니다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>초원지역입니다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>용암지역입니다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound_Map_2</t>
+  </si>
+  <si>
+    <t>Sound_Map_3</t>
+  </si>
+  <si>
+    <t>ClearRewardID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab_GridMap_01</t>
+  </si>
+  <si>
+    <t>BattleType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Raid</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapInfo</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpawnInfo</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterID_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnInfo_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnInfo_02</t>
+  </si>
+  <si>
+    <t>SpawnInfo_03</t>
+  </si>
+  <si>
+    <t>SpawnInfo_04</t>
+  </si>
+  <si>
+    <t>SpawnInfo_05</t>
+  </si>
+  <si>
+    <t>!BattleType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>레이드보스(악마)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>악마 레이드</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnCount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterID_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterID_03</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalCount_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterCount_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalTime_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterCount_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalCount_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalTime_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterCount_03</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalCount_03</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalTime_03</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>Name</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!ID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>초원</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>BGM</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sound_Map_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>빙하</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>용암</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>빙하지역입니다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>초원지역입니다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>용암지역입니다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sound_Map_2</t>
-  </si>
-  <si>
-    <t>Sound_Map_3</t>
-  </si>
-  <si>
-    <t>ClearRewardID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefab_GridMap_01</t>
-  </si>
-  <si>
-    <t>BattleType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Raid</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterSpawnInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterID_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnInfo_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnInfo_02</t>
-  </si>
-  <si>
-    <t>SpawnInfo_03</t>
-  </si>
-  <si>
-    <t>SpawnInfo_04</t>
-  </si>
-  <si>
-    <t>SpawnInfo_05</t>
-  </si>
-  <si>
-    <t>!BattleType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>레이드보스(악마)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>악마 레이드</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnCount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterID_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterID_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalCount_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterCount_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalTime_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterCount_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalCount_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalTime_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterCount_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalCount_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalTime_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -723,17 +723,17 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -771,53 +771,53 @@
   <sheetData>
     <row r="1" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C1" s="10"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="H2" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="9" t="s">
-        <v>32</v>
-      </c>
       <c r="N2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
@@ -826,43 +826,43 @@
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
@@ -873,19 +873,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H4" s="2">
         <v>5</v>
@@ -911,19 +911,19 @@
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5" s="2">
         <v>5</v>
@@ -949,19 +949,19 @@
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6" s="2">
         <v>5</v>
@@ -987,19 +987,19 @@
         <v>4</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -1047,52 +1047,52 @@
   <sheetData>
     <row r="1" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="I2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="L2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -1103,43 +1103,43 @@
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="50">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -104,10 +104,6 @@
     <t>Sound_Map_3</t>
   </si>
   <si>
-    <t>ClearRewardID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Prefab_GridMap_01</t>
   </si>
   <si>
@@ -220,6 +216,14 @@
   </si>
   <si>
     <t>Name</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClearRewardIDs</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001;10002;20001;20002;30001;40001</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -699,7 +703,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -723,17 +727,17 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -762,7 +766,7 @@
     <col min="8" max="8" width="13.75" style="2" customWidth="1"/>
     <col min="9" max="9" width="17.625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="17.625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="16.5" style="2" customWidth="1"/>
+    <col min="14" max="14" width="35.875" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.75" style="2" customWidth="1"/>
     <col min="16" max="16" width="13.625" style="2" customWidth="1"/>
     <col min="17" max="17" width="18.5" style="2" customWidth="1"/>
@@ -774,7 +778,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1" s="10"/>
     </row>
@@ -784,13 +788,13 @@
         <v>3</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>8</v>
@@ -799,25 +803,25 @@
         <v>9</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I2" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="9" t="s">
-        <v>31</v>
-      </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
@@ -835,7 +839,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>2</v>
@@ -844,22 +848,22 @@
         <v>2</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N3" s="9" t="s">
         <v>5</v>
@@ -879,10 +883,10 @@
         <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>10</v>
@@ -904,6 +908,9 @@
       </c>
       <c r="M4" s="2">
         <v>4</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
@@ -917,10 +924,10 @@
         <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>16</v>
@@ -942,6 +949,9 @@
       </c>
       <c r="M5" s="2">
         <v>4</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -955,10 +965,10 @@
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
@@ -980,6 +990,9 @@
       </c>
       <c r="M6" s="2">
         <v>4</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -987,16 +1000,16 @@
         <v>4</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>17</v>
@@ -1050,7 +1063,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
@@ -1059,40 +1072,40 @@
         <v>3</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="I2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>45</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>46</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -1106,40 +1119,40 @@
         <v>5</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -1168,23 +1168,9 @@
         <v>10001</v>
       </c>
       <c r="D4" s="2">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>10002</v>
-      </c>
-      <c r="H4" s="2">
         <v>30</v>
       </c>
-      <c r="I4" s="2">
-        <v>5</v>
-      </c>
+      <c r="G4"/>
       <c r="K4"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -1195,32 +1181,15 @@
         <v>10001</v>
       </c>
       <c r="D5" s="2">
-        <v>70</v>
-      </c>
-      <c r="E5" s="2">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G5">
         <v>10002</v>
       </c>
       <c r="H5" s="2">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>10003</v>
-      </c>
-      <c r="L5" s="2">
-        <v>15</v>
-      </c>
-      <c r="M5" s="2">
-        <v>5</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="K5"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
@@ -1230,33 +1199,20 @@
         <v>10001</v>
       </c>
       <c r="D6" s="2">
-        <v>150</v>
-      </c>
-      <c r="E6" s="2">
-        <v>15</v>
-      </c>
-      <c r="F6" s="2">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G6">
         <v>10002</v>
       </c>
       <c r="H6" s="2">
-        <v>50</v>
-      </c>
-      <c r="I6" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K6">
         <v>10003</v>
       </c>
       <c r="L6" s="2">
-        <v>30</v>
-      </c>
-      <c r="M6" s="2">
-        <v>5</v>
-      </c>
-      <c r="N6"/>
+        <v>10</v>
+      </c>
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
     </row>
@@ -1268,19 +1224,19 @@
         <v>10001</v>
       </c>
       <c r="D7" s="2">
-        <v>200</v>
-      </c>
-      <c r="E7" s="2">
-        <v>15</v>
-      </c>
-      <c r="F7" s="2">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G7" s="5">
         <v>30001</v>
       </c>
       <c r="H7" s="2">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>10003</v>
+      </c>
+      <c r="L7" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -703,7 +703,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -892,22 +892,16 @@
         <v>10</v>
       </c>
       <c r="H4" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
       </c>
       <c r="J4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="2">
-        <v>2</v>
-      </c>
-      <c r="L4" s="2">
         <v>3</v>
-      </c>
-      <c r="M4" s="2">
-        <v>4</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>49</v>
@@ -1187,7 +1181,7 @@
         <v>10002</v>
       </c>
       <c r="H5" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K5"/>
     </row>
@@ -1205,13 +1199,13 @@
         <v>10002</v>
       </c>
       <c r="H6" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>10003</v>
       </c>
       <c r="L6" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
@@ -1230,13 +1224,13 @@
         <v>30001</v>
       </c>
       <c r="H7" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K7">
         <v>10003</v>
       </c>
       <c r="L7" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,12 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
     <sheet name="#MapInfo" sheetId="13" r:id="rId2"/>
     <sheet name="#MonsterSpawnInfo" sheetId="14" r:id="rId3"/>
+    <sheet name="#Dungeon" sheetId="18" r:id="rId4"/>
+    <sheet name="#StageGroup" sheetId="16" r:id="rId5"/>
+    <sheet name="#Stage" sheetId="17" r:id="rId6"/>
+    <sheet name="#MapData" sheetId="15" r:id="rId7"/>
+    <sheet name="#MonsterSpawn" sheetId="21" r:id="rId8"/>
+    <sheet name="#DropObject" sheetId="19" r:id="rId9"/>
+    <sheet name="#StageReward" sheetId="20" r:id="rId10"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -31,200 +38,650 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>양대용</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>Defense : 웨이브 수
+BuildingDestroy : 파괴할 건물 수
+Capture : 점령 유지 시간
+Breakthrought : x
+BossBattle : 죽여야하는 보스의 수</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="148">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>초원</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound_Map_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>빙하</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>용암</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound_Map_2</t>
+  </si>
+  <si>
+    <t>Sound_Map_3</t>
+  </si>
+  <si>
+    <t>Prefab_GridMap_01</t>
+  </si>
+  <si>
+    <t>BattleType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wave</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Raid</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpawnInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterID_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnInfo_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnInfo_02</t>
+  </si>
+  <si>
+    <t>SpawnInfo_03</t>
+  </si>
+  <si>
+    <t>SpawnInfo_04</t>
+  </si>
+  <si>
+    <t>SpawnInfo_05</t>
+  </si>
+  <si>
+    <t>!BattleType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnCount</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterID_02</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterID_03</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalCount_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterCount_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalTime_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterCount_02</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalCount_02</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalTime_02</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterCount_03</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalCount_03</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>IntervalTime_03</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClearRewardIDs</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001;10002;20001;20002;30001;40001</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>지옥</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapData</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapModeType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingDestroy</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defense</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Capture</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakthrough</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossBattle</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!MapModeType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModeType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>BGM</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sound_Map_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>빙하</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>용암</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>빙하지역입니다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>초원지역입니다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>용암지역입니다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sound_Map_2</t>
-  </si>
-  <si>
-    <t>Sound_Map_3</t>
-  </si>
-  <si>
-    <t>Prefab_GridMap_01</t>
-  </si>
-  <si>
-    <t>BattleType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Raid</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterSpawnInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterID_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnInfo_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnInfo_02</t>
-  </si>
-  <si>
-    <t>SpawnInfo_03</t>
-  </si>
-  <si>
-    <t>SpawnInfo_04</t>
-  </si>
-  <si>
-    <t>SpawnInfo_05</t>
-  </si>
-  <si>
-    <t>!BattleType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>레이드보스(악마)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>악마 레이드</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClearValue</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>LimitTime</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Table</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초원</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dungeon</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>고블린 숲 1-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>고블린 숲 1-2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>고블린 숲 1-3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>TotalStageCount</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageGroup</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExtraStageGroupID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageID_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageID_2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageID_3</t>
+  </si>
+  <si>
+    <t>StageID_4</t>
+  </si>
+  <si>
+    <t>StageID_5</t>
+  </si>
+  <si>
+    <t>StageGroupID_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageGroupID_2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageGroupID_3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageGroupID_4</t>
+  </si>
+  <si>
+    <t>StageGroupID_5</t>
+  </si>
+  <si>
+    <t>건물 파괴 1-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>디펜스 1-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>디펜스 1-2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>디펜스 1-3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>건물 파괴 1-2</t>
+  </si>
+  <si>
+    <t>건물 파괴 1-3</t>
+  </si>
+  <si>
+    <t>점령 1-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>점령 1-2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>점령 1-3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌파 1-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌파 1-2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌파 1-3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스전 1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapObjectIDs</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>던전1의  스테이지1 그룹</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>던전1의  스테이지2 그룹</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>던전1의  스테이지3 그룹</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>던전1의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 추가 스테이지 그룹</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HealOrb</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaOrb</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageReward</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropObject</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageRewardIDs</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력 회복 구슬</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미너 회복 구슬</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MagicEssence</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArcaneScroll</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>비전 주문서</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마력정수</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!MonsterTypes</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elite</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boss</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropChance</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinCount</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxCount</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>카드 구매창이 뜨게 하는 스크롤</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력을 25% 회복시키는 오브</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미너를 25% 회복 시키는 오브</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>카드구매용 임시재화</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 웨이브가 n번 오고 모두 섬멸</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>지정된 공간에서 n초 동안 버티면 승리</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 저자선을 뚫고 지정된 위치로 이동하면 승리</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스를 n마리 죽이면 승리</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>지정된 건물을 n개 파괴하면 승리</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력 25% 회복</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미너 25% 회복</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 구매 재화</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 구매 목록</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>GroupID</t>
+  </si>
+  <si>
+    <t>GroupID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropObjectGroupID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001;10002</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpawn</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpawnGroupIDs</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>SpawnCount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterID_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterID_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalCount_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterCount_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalTime_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterCount_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalCount_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalTime_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterCount_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalCount_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalTime_03</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnPoint</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnDelay</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClearRewardIDs</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001;10002;20001;20002;30001;40001</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnPoint_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnPoint_02</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnPoint_03</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>40001;40002;40003</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropObjectType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!DropObjectType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -234,12 +691,28 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -291,6 +764,29 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -384,12 +880,12 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -403,31 +899,66 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -703,7 +1234,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -711,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="1" bestFit="1" customWidth="1"/>
@@ -727,299 +1258,479 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D11" s="2" t="s">
-        <v>1</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="19"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" s="19"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="17.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="18.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4" s="16"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="F5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5" s="16"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6" s="16"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H12" s="16"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="17.625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="35.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.75" style="2" customWidth="1"/>
-    <col min="16" max="16" width="13.625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="18.5" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="15.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="17.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="35.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.75" style="2" customWidth="1"/>
+    <col min="15" max="15" width="13.625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="18.5" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C1" s="10"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>8</v>
-      </c>
       <c r="G2" s="9" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>5</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="N3" s="9"/>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="G4" s="2">
+        <v>3</v>
       </c>
       <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>2</v>
+      </c>
+      <c r="J4" s="2">
         <v>3</v>
       </c>
-      <c r="I4" s="2">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2">
-        <v>2</v>
-      </c>
-      <c r="K4" s="2">
-        <v>3</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="M4" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>16</v>
+      <c r="G5" s="2">
+        <v>5</v>
       </c>
       <c r="H5" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
       </c>
       <c r="J5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2">
-        <v>3</v>
-      </c>
-      <c r="M5" s="2">
         <v>4</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="M5" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="G6" s="2">
+        <v>5</v>
       </c>
       <c r="H6" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
       </c>
       <c r="J6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2">
-        <v>3</v>
-      </c>
-      <c r="M6" s="2">
         <v>4</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="M6" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>4</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
       </c>
       <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C8" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1054,52 +1765,52 @@
   <sheetData>
     <row r="1" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -1110,43 +1821,43 @@
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O3" s="9"/>
       <c r="P3" s="9"/>
@@ -1300,7 +2011,2442 @@
       <c r="J18" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="17.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="18.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>10001</v>
+      </c>
+      <c r="G4" s="2">
+        <v>10002</v>
+      </c>
+      <c r="H4" s="2">
+        <v>10003</v>
+      </c>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4" s="16">
+        <v>10004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="2">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>10001</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10002</v>
+      </c>
+      <c r="H5" s="2">
+        <v>10003</v>
+      </c>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5" s="16">
+        <v>10004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>10001</v>
+      </c>
+      <c r="G6" s="2">
+        <v>10002</v>
+      </c>
+      <c r="H6" s="2">
+        <v>10003</v>
+      </c>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6" s="16">
+        <v>10004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H10" s="16"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H12" s="16"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.625" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="17.375" style="16" customWidth="1"/>
+    <col min="8" max="8" width="24" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.5" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="16">
+        <v>10001</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="2">
+        <v>10001</v>
+      </c>
+      <c r="E4" s="2">
+        <v>20001</v>
+      </c>
+      <c r="F4" s="2">
+        <v>30001</v>
+      </c>
+      <c r="G4" s="2">
+        <v>40001</v>
+      </c>
+      <c r="H4" s="17"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="16">
+        <v>10002</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="2">
+        <v>10002</v>
+      </c>
+      <c r="E5" s="2">
+        <v>20002</v>
+      </c>
+      <c r="F5" s="2">
+        <v>30002</v>
+      </c>
+      <c r="G5" s="2">
+        <v>40002</v>
+      </c>
+      <c r="H5" s="17"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="16">
+        <v>10003</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="2">
+        <v>10003</v>
+      </c>
+      <c r="E6" s="2">
+        <v>20003</v>
+      </c>
+      <c r="F6" s="2">
+        <v>30003</v>
+      </c>
+      <c r="G6" s="2">
+        <v>40003</v>
+      </c>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="16">
+        <v>10004</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="16">
+        <v>50001</v>
+      </c>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I8" s="11"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E14" s="11"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E16" s="11"/>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="E17" s="11"/>
+    </row>
+    <row r="18" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D18" s="2"/>
+      <c r="E18" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="17.375" style="2" customWidth="1"/>
+    <col min="6" max="8" width="15.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="19.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="J1" s="22"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>10001</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="H4" s="2">
+        <v>10001</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="K4">
+        <v>2001</v>
+      </c>
+      <c r="L4"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>10002</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2">
+        <v>10001</v>
+      </c>
+      <c r="J5" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="K5">
+        <v>2001</v>
+      </c>
+      <c r="L5"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>10003</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2">
+        <v>10001</v>
+      </c>
+      <c r="J6" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="K6">
+        <v>2001</v>
+      </c>
+      <c r="L6"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>20001</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>300</v>
+      </c>
+      <c r="H7" s="2">
+        <v>10001</v>
+      </c>
+      <c r="J7" s="24">
+        <v>20001</v>
+      </c>
+      <c r="K7">
+        <v>1001</v>
+      </c>
+      <c r="L7"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>20002</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>300</v>
+      </c>
+      <c r="H8" s="2">
+        <v>10001</v>
+      </c>
+      <c r="J8" s="24">
+        <v>20001</v>
+      </c>
+      <c r="K8">
+        <v>1001</v>
+      </c>
+      <c r="L8"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>20003</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>300</v>
+      </c>
+      <c r="H9" s="2">
+        <v>10001</v>
+      </c>
+      <c r="J9" s="24">
+        <v>20001</v>
+      </c>
+      <c r="K9">
+        <v>1001</v>
+      </c>
+      <c r="L9"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>30001</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10">
+        <v>30</v>
+      </c>
+      <c r="G10" s="2">
+        <v>300</v>
+      </c>
+      <c r="H10" s="2">
+        <v>10001</v>
+      </c>
+      <c r="J10" s="25">
+        <v>30001</v>
+      </c>
+      <c r="K10">
+        <v>2001</v>
+      </c>
+      <c r="L10"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>30002</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>30</v>
+      </c>
+      <c r="G11" s="2">
+        <v>300</v>
+      </c>
+      <c r="H11" s="2">
+        <v>10001</v>
+      </c>
+      <c r="J11" s="25">
+        <v>30001</v>
+      </c>
+      <c r="K11">
+        <v>2001</v>
+      </c>
+      <c r="L11"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>30003</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <v>30</v>
+      </c>
+      <c r="G12" s="2">
+        <v>300</v>
+      </c>
+      <c r="H12" s="2">
+        <v>10001</v>
+      </c>
+      <c r="J12" s="25">
+        <v>30001</v>
+      </c>
+      <c r="K12">
+        <v>2001</v>
+      </c>
+      <c r="L12"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>40001</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13"/>
+      <c r="H13" s="2">
+        <v>10001</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="K13">
+        <v>1001</v>
+      </c>
+      <c r="L13"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>40002</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14"/>
+      <c r="H14" s="2">
+        <v>10001</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="K14">
+        <v>1001</v>
+      </c>
+      <c r="L14"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>40003</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15"/>
+      <c r="H15" s="2">
+        <v>10001</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="K15">
+        <v>1001</v>
+      </c>
+      <c r="L15"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <v>50001</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2">
+        <v>10001</v>
+      </c>
+      <c r="J16" s="26">
+        <v>50001</v>
+      </c>
+      <c r="K16">
+        <v>3001</v>
+      </c>
+      <c r="L16"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="K18"/>
+      <c r="L18"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="I20"/>
+      <c r="J20" s="27"/>
+      <c r="K20"/>
+      <c r="L20"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21"/>
+      <c r="I21"/>
+      <c r="J21" s="27"/>
+      <c r="K21"/>
+      <c r="L21"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="I22"/>
+      <c r="J22" s="27"/>
+      <c r="K22"/>
+      <c r="L22"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23"/>
+      <c r="I23"/>
+      <c r="J23" s="27"/>
+      <c r="K23"/>
+      <c r="L23"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="I24" s="5"/>
+      <c r="J24" s="27"/>
+      <c r="K24"/>
+      <c r="L24"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25"/>
+      <c r="J25" s="27"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="J26" s="27"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="J27" s="27"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="J28" s="27"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="18.5" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="10"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>10001</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>20001</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>30001</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>40001</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C13" s="11"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="11"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C15" s="11"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C16" s="11"/>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C17" s="11"/>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C18" s="11"/>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C19" s="11"/>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C20" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.375" customWidth="1"/>
+    <col min="4" max="6" width="17.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>10001</v>
+      </c>
+      <c r="D4">
+        <v>10001</v>
+      </c>
+      <c r="E4">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>10001</v>
+      </c>
+      <c r="D5">
+        <v>10002</v>
+      </c>
+      <c r="E5" s="2">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>10002</v>
+      </c>
+      <c r="D6">
+        <v>10001</v>
+      </c>
+      <c r="E6">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>10002</v>
+      </c>
+      <c r="D7">
+        <v>10002</v>
+      </c>
+      <c r="E7" s="2">
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>10002</v>
+      </c>
+      <c r="D8">
+        <v>10003</v>
+      </c>
+      <c r="E8" s="2">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>20001</v>
+      </c>
+      <c r="D9">
+        <v>10001</v>
+      </c>
+      <c r="E9" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>7</v>
+      </c>
+      <c r="C10">
+        <v>20001</v>
+      </c>
+      <c r="D10">
+        <v>10002</v>
+      </c>
+      <c r="E10" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F10" t="s">
+        <v>142</v>
+      </c>
+      <c r="G10" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>8</v>
+      </c>
+      <c r="C11">
+        <v>20001</v>
+      </c>
+      <c r="D11">
+        <v>10003</v>
+      </c>
+      <c r="E11" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F11" t="s">
+        <v>142</v>
+      </c>
+      <c r="G11" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>20001</v>
+      </c>
+      <c r="D12" s="2">
+        <v>20001</v>
+      </c>
+      <c r="E12" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F12" t="s">
+        <v>142</v>
+      </c>
+      <c r="G12" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>30001</v>
+      </c>
+      <c r="D13">
+        <v>10001</v>
+      </c>
+      <c r="E13" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F13" t="s">
+        <v>142</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>30001</v>
+      </c>
+      <c r="D14">
+        <v>10002</v>
+      </c>
+      <c r="E14" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G14" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>30001</v>
+      </c>
+      <c r="D15">
+        <v>10003</v>
+      </c>
+      <c r="E15" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F15" t="s">
+        <v>142</v>
+      </c>
+      <c r="G15" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>40001</v>
+      </c>
+      <c r="D16">
+        <v>10001</v>
+      </c>
+      <c r="E16" s="2">
+        <v>50</v>
+      </c>
+      <c r="F16" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>40002</v>
+      </c>
+      <c r="D17">
+        <v>10001</v>
+      </c>
+      <c r="E17" s="2">
+        <v>50</v>
+      </c>
+      <c r="F17" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>40003</v>
+      </c>
+      <c r="D18">
+        <v>10001</v>
+      </c>
+      <c r="E18" s="2">
+        <v>50</v>
+      </c>
+      <c r="F18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="2">
+        <v>16</v>
+      </c>
+      <c r="C19">
+        <v>50001</v>
+      </c>
+      <c r="D19" s="2">
+        <v>50001</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J35"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="17.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="17.375" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4">
+        <v>1001</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="2">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5">
+        <v>1001</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="2">
+        <v>15</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6">
+        <v>1001</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H6" s="2">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>4</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7">
+        <v>1001</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H7" s="2">
+        <v>5</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>5</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8">
+        <v>1001</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H8" s="2">
+        <v>15</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>6</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9">
+        <v>1001</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H9" s="2">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>7</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10">
+        <v>1001</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" s="2">
+        <v>100</v>
+      </c>
+      <c r="I10" s="2">
+        <v>10</v>
+      </c>
+      <c r="J10" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>8</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11">
+        <v>1001</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H11" s="2">
+        <v>100</v>
+      </c>
+      <c r="I11" s="2">
+        <v>50</v>
+      </c>
+      <c r="J11" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>9</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12">
+        <v>1001</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H12" s="2">
+        <v>100</v>
+      </c>
+      <c r="I12" s="2">
+        <v>300</v>
+      </c>
+      <c r="J12" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E13">
+        <v>1001</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E14">
+        <v>1001</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H14" s="2">
+        <v>15</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E15">
+        <v>1001</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" s="2">
+        <v>100</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <v>13</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16">
+        <v>2001</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <v>14</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17">
+        <v>2001</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H17" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <v>15</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E18">
+        <v>2001</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" s="2">
+        <v>100</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="2">
+        <v>16</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19">
+        <v>2001</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H19" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <v>17</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20">
+        <v>2001</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H20" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="I20" s="2">
+        <v>1</v>
+      </c>
+      <c r="J20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B21" s="2">
+        <v>18</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21">
+        <v>2001</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H21" s="2">
+        <v>100</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>19</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22">
+        <v>2001</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H22" s="2">
+        <v>100</v>
+      </c>
+      <c r="I22" s="2">
+        <v>5</v>
+      </c>
+      <c r="J22" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B23" s="2">
+        <v>20</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23">
+        <v>2001</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H23" s="2">
+        <v>100</v>
+      </c>
+      <c r="I23" s="2">
+        <v>25</v>
+      </c>
+      <c r="J23" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <v>21</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E24">
+        <v>2001</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H24" s="2">
+        <v>100</v>
+      </c>
+      <c r="I24" s="2">
+        <v>300</v>
+      </c>
+      <c r="J24" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B25" s="2">
+        <v>22</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25">
+        <v>2001</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B26" s="2">
+        <v>23</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26">
+        <v>2001</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H26" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B27" s="2">
+        <v>24</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27">
+        <v>2001</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H27" s="2">
+        <v>100</v>
+      </c>
+      <c r="I27" s="2">
+        <v>1</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B28" s="2">
+        <v>25</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28">
+        <v>3001</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H28" s="2">
+        <v>100</v>
+      </c>
+      <c r="I28" s="2">
+        <v>1</v>
+      </c>
+      <c r="J28" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B29" s="2">
+        <v>26</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29">
+        <v>3001</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H29" s="2">
+        <v>100</v>
+      </c>
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
+        <v>27</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30">
+        <v>3001</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H30" s="2">
+        <v>100</v>
+      </c>
+      <c r="I30" s="2">
+        <v>300</v>
+      </c>
+      <c r="J30" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B31" s="2">
+        <v>28</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E31">
+        <v>3001</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H31" s="2">
+        <v>100</v>
+      </c>
+      <c r="I31" s="2">
+        <v>1</v>
+      </c>
+      <c r="J31" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B32" s="2">
+        <v>29</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32">
+        <v>3001</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H32" s="2">
+        <v>100</v>
+      </c>
+      <c r="I32" s="2">
+        <v>1</v>
+      </c>
+      <c r="J32" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B33" s="2">
+        <v>30</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E33">
+        <v>3001</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H33" s="2">
+        <v>100</v>
+      </c>
+      <c r="I33" s="2">
+        <v>1</v>
+      </c>
+      <c r="J33" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B34" s="2">
+        <v>31</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E34">
+        <v>3001</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H34" s="2">
+        <v>100</v>
+      </c>
+      <c r="I34" s="2">
+        <v>300</v>
+      </c>
+      <c r="J34" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B35" s="2">
+        <v>32</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E35">
+        <v>3001</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H35" s="2">
+        <v>100</v>
+      </c>
+      <c r="I35" s="2">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="8"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="156">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="8" type="noConversion"/>
@@ -324,22 +324,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Dungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린 숲 1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린 숲 1-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>고블린 숲 1-3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>TotalStageCount</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -681,6 +665,53 @@
   </si>
   <si>
     <t>!DropObjectType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecommandedLvText</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 ~ 5</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>5 ~ 10</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>10 ~ 15</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 고블린 숲 1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 고블린 숲 2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 고블린 숲 3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dungeon</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Image_Stage_1</t>
+  </si>
+  <si>
+    <t>Image_Stage_2</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -885,7 +916,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -959,6 +990,9 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1234,7 +1268,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1285,7 +1319,7 @@
         <v>49</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1293,7 +1327,7 @@
         <v>48</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1301,7 +1335,7 @@
         <v>50</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1309,7 +1343,7 @@
         <v>51</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1317,7 +1351,7 @@
         <v>52</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1325,40 +1359,40 @@
         <v>0</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D12" s="19"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1386,7 +1420,7 @@
         <v>60</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -1398,7 +1432,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -1414,7 +1448,7 @@
         <v>45</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -1430,7 +1464,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4"/>
@@ -1444,7 +1478,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D5" s="11"/>
       <c r="F5"/>
@@ -1457,7 +1491,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6"/>
@@ -2018,30 +2052,34 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="17.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="18.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="19.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="18.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="18.5" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>62</v>
+      <c r="B1" s="28" t="s">
+        <v>152</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="9" t="s">
         <v>2</v>
@@ -2053,28 +2091,34 @@
         <v>55</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="F2" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L2" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M2" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="2" t="s">
         <v>45</v>
@@ -2086,10 +2130,10 @@
         <v>56</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>45</v>
+        <v>144</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>45</v>
+        <v>144</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>45</v>
@@ -2106,93 +2150,117 @@
       <c r="K3" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>63</v>
+        <v>149</v>
       </c>
       <c r="D4" s="11"/>
-      <c r="E4">
+      <c r="E4" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4">
         <v>3</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>10001</v>
       </c>
-      <c r="G4" s="2">
+      <c r="I4" s="2">
         <v>10002</v>
       </c>
-      <c r="H4" s="2">
+      <c r="J4" s="2">
         <v>10003</v>
       </c>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4" s="16">
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4" s="16">
         <v>10004</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="D5" s="11"/>
-      <c r="E5" s="2">
+      <c r="E5" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="G5" s="2">
         <v>3</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>10001</v>
       </c>
-      <c r="G5" s="2">
+      <c r="I5" s="2">
         <v>10002</v>
       </c>
-      <c r="H5" s="2">
+      <c r="J5" s="2">
         <v>10003</v>
       </c>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5" s="16">
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5" s="16">
         <v>10004</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="D6" s="11"/>
-      <c r="E6">
+      <c r="E6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G6">
         <v>3</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>10001</v>
       </c>
-      <c r="G6" s="2">
+      <c r="I6" s="2">
         <v>10002</v>
       </c>
-      <c r="H6" s="2">
+      <c r="J6" s="2">
         <v>10003</v>
       </c>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6" s="16">
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6" s="16">
         <v>10004</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H10" s="16"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H12" s="16"/>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J10" s="16"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J11" s="16"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J12" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -2222,7 +2290,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -2241,19 +2309,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" s="17" t="s">
         <v>70</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>74</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -2267,19 +2335,19 @@
         <v>1</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
@@ -2289,7 +2357,7 @@
         <v>10001</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D4" s="2">
         <v>10001</v>
@@ -2310,7 +2378,7 @@
         <v>10002</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D5" s="2">
         <v>10002</v>
@@ -2331,7 +2399,7 @@
         <v>10003</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D6" s="2">
         <v>10003</v>
@@ -2352,7 +2420,7 @@
         <v>10004</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D7" s="16">
         <v>50001</v>
@@ -2436,16 +2504,16 @@
         <v>57</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="J2" s="23" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -2489,7 +2557,7 @@
         <v>10001</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" t="s">
@@ -2502,7 +2570,7 @@
         <v>10001</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K4">
         <v>2001</v>
@@ -2514,7 +2582,7 @@
         <v>10002</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" t="s">
@@ -2527,7 +2595,7 @@
         <v>10001</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K5">
         <v>2001</v>
@@ -2539,7 +2607,7 @@
         <v>10003</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" t="s">
@@ -2552,7 +2620,7 @@
         <v>10001</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K6">
         <v>2001</v>
@@ -2564,7 +2632,7 @@
         <v>20001</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="2" t="s">
@@ -2592,7 +2660,7 @@
         <v>20002</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="2" t="s">
@@ -2620,7 +2688,7 @@
         <v>20003</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="2" t="s">
@@ -2648,7 +2716,7 @@
         <v>30001</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" t="s">
@@ -2676,7 +2744,7 @@
         <v>30002</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" t="s">
@@ -2704,7 +2772,7 @@
         <v>30003</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" t="s">
@@ -2732,7 +2800,7 @@
         <v>40001</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" t="s">
@@ -2743,7 +2811,7 @@
         <v>10001</v>
       </c>
       <c r="J13" s="25" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K13">
         <v>1001</v>
@@ -2755,7 +2823,7 @@
         <v>40002</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" t="s">
@@ -2766,7 +2834,7 @@
         <v>10001</v>
       </c>
       <c r="J14" s="25" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K14">
         <v>1001</v>
@@ -2778,7 +2846,7 @@
         <v>40003</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" t="s">
@@ -2789,7 +2857,7 @@
         <v>10001</v>
       </c>
       <c r="J15" s="25" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K15">
         <v>1001</v>
@@ -2801,7 +2869,7 @@
         <v>50001</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" t="s">
@@ -3063,7 +3131,7 @@
         <v>60</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -3076,19 +3144,19 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -3109,7 +3177,7 @@
         <v>56</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3126,7 +3194,7 @@
         <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G4"/>
     </row>
@@ -3144,7 +3212,7 @@
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G5"/>
     </row>
@@ -3162,7 +3230,7 @@
         <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G6"/>
     </row>
@@ -3180,7 +3248,7 @@
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3197,7 +3265,7 @@
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -3214,7 +3282,7 @@
         <v>9999</v>
       </c>
       <c r="F9" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -3234,7 +3302,7 @@
         <v>9999</v>
       </c>
       <c r="F10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G10" s="2">
         <v>3</v>
@@ -3254,7 +3322,7 @@
         <v>9999</v>
       </c>
       <c r="F11" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G11" s="2">
         <v>5</v>
@@ -3274,7 +3342,7 @@
         <v>9999</v>
       </c>
       <c r="F12" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G12" s="2">
         <v>10</v>
@@ -3294,7 +3362,7 @@
         <v>9999</v>
       </c>
       <c r="F13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -3314,7 +3382,7 @@
         <v>9999</v>
       </c>
       <c r="F14" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G14" s="2">
         <v>3</v>
@@ -3334,7 +3402,7 @@
         <v>9999</v>
       </c>
       <c r="F15" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G15" s="2">
         <v>5</v>
@@ -3354,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="F16" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
@@ -3371,7 +3439,7 @@
         <v>50</v>
       </c>
       <c r="F17" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
@@ -3388,7 +3456,7 @@
         <v>50</v>
       </c>
       <c r="F18" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
@@ -3405,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
@@ -3447,7 +3515,7 @@
         <v>60</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -3469,22 +3537,22 @@
         <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -3502,13 +3570,13 @@
         <v>45</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I3" s="9" t="s">
         <v>45</v>
@@ -3522,19 +3590,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E4">
         <v>1001</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H4" s="2">
         <v>5</v>
@@ -3551,19 +3619,19 @@
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E5">
         <v>1001</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H5" s="2">
         <v>15</v>
@@ -3580,19 +3648,19 @@
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E6">
         <v>1001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H6" s="2">
         <v>100</v>
@@ -3609,19 +3677,19 @@
         <v>4</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E7">
         <v>1001</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H7" s="2">
         <v>5</v>
@@ -3638,19 +3706,19 @@
         <v>5</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E8">
         <v>1001</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H8" s="2">
         <v>15</v>
@@ -3667,19 +3735,19 @@
         <v>6</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E9">
         <v>1001</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H9" s="2">
         <v>100</v>
@@ -3696,19 +3764,19 @@
         <v>7</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E10">
         <v>1001</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H10" s="2">
         <v>100</v>
@@ -3725,19 +3793,19 @@
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E11">
         <v>1001</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H11" s="2">
         <v>100</v>
@@ -3754,19 +3822,19 @@
         <v>9</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E12">
         <v>1001</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H12" s="2">
         <v>100</v>
@@ -3783,19 +3851,19 @@
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E13">
         <v>1001</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -3812,19 +3880,19 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E14">
         <v>1001</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H14" s="2">
         <v>15</v>
@@ -3841,19 +3909,19 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E15">
         <v>1001</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H15" s="2">
         <v>100</v>
@@ -3870,19 +3938,19 @@
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E16">
         <v>2001</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H16" s="2">
         <v>2.5</v>
@@ -3899,19 +3967,19 @@
         <v>14</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E17">
         <v>2001</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H17" s="2">
         <v>7.5</v>
@@ -3928,19 +3996,19 @@
         <v>15</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E18">
         <v>2001</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H18" s="2">
         <v>100</v>
@@ -3957,19 +4025,19 @@
         <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E19">
         <v>2001</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H19" s="2">
         <v>2.5</v>
@@ -3986,19 +4054,19 @@
         <v>17</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E20">
         <v>2001</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H20" s="2">
         <v>7.5</v>
@@ -4015,19 +4083,19 @@
         <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E21">
         <v>2001</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H21" s="2">
         <v>100</v>
@@ -4044,19 +4112,19 @@
         <v>19</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E22">
         <v>2001</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H22" s="2">
         <v>100</v>
@@ -4073,19 +4141,19 @@
         <v>20</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E23">
         <v>2001</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H23" s="2">
         <v>100</v>
@@ -4102,19 +4170,19 @@
         <v>21</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E24">
         <v>2001</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H24" s="2">
         <v>100</v>
@@ -4131,19 +4199,19 @@
         <v>22</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E25">
         <v>2001</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H25" s="2">
         <v>0.5</v>
@@ -4160,19 +4228,19 @@
         <v>23</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E26">
         <v>2001</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H26" s="2">
         <v>7.5</v>
@@ -4189,19 +4257,19 @@
         <v>24</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E27">
         <v>2001</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H27" s="2">
         <v>100</v>
@@ -4218,19 +4286,19 @@
         <v>25</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E28">
         <v>3001</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H28" s="2">
         <v>100</v>
@@ -4247,19 +4315,19 @@
         <v>26</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E29">
         <v>3001</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H29" s="2">
         <v>100</v>
@@ -4276,19 +4344,19 @@
         <v>27</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E30">
         <v>3001</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H30" s="2">
         <v>100</v>
@@ -4305,19 +4373,19 @@
         <v>28</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E31">
         <v>3001</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H31" s="2">
         <v>100</v>
@@ -4334,19 +4402,19 @@
         <v>29</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E32">
         <v>3001</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H32" s="2">
         <v>100</v>
@@ -4363,19 +4431,19 @@
         <v>30</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E33">
         <v>3001</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H33" s="2">
         <v>100</v>
@@ -4392,19 +4460,19 @@
         <v>31</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E34">
         <v>3001</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H34" s="2">
         <v>100</v>
@@ -4421,19 +4489,19 @@
         <v>32</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E35">
         <v>3001</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H35" s="2">
         <v>100</v>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -68,50 +68,50 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="164">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>초원</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MapPrefab</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>BGM</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Sound_Map_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>빙하</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>용암</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Sound_Map_2</t>
@@ -124,35 +124,35 @@
   </si>
   <si>
     <t>BattleType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Wave</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Raid</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MapInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterSpawnInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterID_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SpawnInfo_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SpawnInfo_02</t>
@@ -168,139 +168,119 @@
   </si>
   <si>
     <t>!BattleType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SpawnCount</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterID_02</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterID_03</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>IntervalCount_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterCount_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>IntervalTime_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterCount_02</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>IntervalCount_02</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>IntervalTime_02</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterCount_03</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>IntervalCount_03</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>IntervalTime_03</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ClearRewardIDs</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>10001;10002;20001;20002;30001;40001</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>지옥</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Stage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapData</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MapModeType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>BuildingDestroy</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Defense</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Capture</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Breakthrough</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>BossBattle</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!MapModeType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ModeType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClearValue</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>LimitTime</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -317,23 +297,15 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>초원</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>TotalStageCount</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageGroup</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExtraStageGroupID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -349,15 +321,15 @@
       </rPr>
       <t>int</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageID_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageID_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageID_3</t>
@@ -369,16 +341,12 @@
     <t>StageID_5</t>
   </si>
   <si>
-    <t>StageGroupID_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>StageGroupID_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageGroupID_3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageGroupID_4</t>
@@ -388,19 +356,19 @@
   </si>
   <si>
     <t>건물 파괴 1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>디펜스 1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>디펜스 1-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>디펜스 1-3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>건물 파괴 1-2</t>
@@ -410,47 +378,47 @@
   </si>
   <si>
     <t>점령 1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>점령 1-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>점령 1-3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>돌파 1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>돌파 1-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>돌파 1-3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>보스전 1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MapObjectIDs</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>던전1의  스테이지1 그룹</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>던전1의  스테이지2 그룹</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>던전1의  스테이지3 그룹</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -466,253 +434,317 @@
       </rPr>
       <t xml:space="preserve"> 추가 스테이지 그룹</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>HealOrb</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StaminaOrb</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageReward</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DropObject</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageRewardIDs</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>체력 회복 구슬</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>스태미너 회복 구슬</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MagicEssence</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ArcaneScroll</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>비전 주문서</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>마력정수</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!MonsterTypes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Elite</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Boss</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DropChance</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MinCount</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MaxCount</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>카드 구매창이 뜨게 하는 스크롤</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>체력을 25% 회복시키는 오브</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>스태미너를 25% 회복 시키는 오브</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>카드구매용 임시재화</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>적 웨이브가 n번 오고 모두 섬멸</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>지정된 공간에서 n초 동안 버티면 승리</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>적 저자선을 뚫고 지정된 위치로 이동하면 승리</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>보스를 n마리 죽이면 승리</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>지정된 건물을 n개 파괴하면 승리</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>체력 25% 회복</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>스태미너 25% 회복</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>스킬 구매 재화</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>스킬 구매 목록</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>GroupID</t>
   </si>
   <si>
     <t>GroupID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DropObjectGroupID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>10001;10002</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterID</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnPoint_01</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnPoint_02</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnPoint_03</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>40001;40002;40003</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropObjectType</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!DropObjectType</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecommandedLvText</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 ~ 5</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>5 ~ 10</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>10 ~ 15</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dungeon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Image_Stage_1</t>
+  </si>
+  <si>
+    <t>Image_Stage_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 고블린 숲(쉬움)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 고블린 숲(보통)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 고블린 숲(어려움)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>TotalStageCount</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageGroupID_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExtraStageGroupID</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModeType</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingDestroy</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Capture</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakthrough</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossBattle</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClearValue</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!MapModeType</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapID</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpawnGroupIDs</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapData</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound_Map_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterSpawn</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterSpawnGroupIDs</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnCount</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SpawnPoint</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnDelay</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnPoint_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnPoint_02</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnPoint_03</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>40001;40002;40003</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DropObjectType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!DropObjectType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>RecommandedLvText</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 ~ 5</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>5 ~ 10</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>10 ~ 15</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 고블린 숲 1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>2. 고블린 숲 2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. 고블린 숲 3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Image_Stage_1</t>
-  </si>
-  <si>
-    <t>Image_Stage_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnStepCount</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnAllCount</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnStepDelay</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -722,12 +754,20 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -911,10 +951,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -930,50 +970,50 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -985,13 +1025,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1268,7 +1308,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1310,48 +1350,48 @@
         <v>0</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="19"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1359,44 +1399,44 @@
         <v>0</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="D12" s="19"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1417,10 +1457,10 @@
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -1432,7 +1472,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -1448,7 +1488,7 @@
         <v>45</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -1464,7 +1504,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4"/>
@@ -1478,7 +1518,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D5" s="11"/>
       <c r="F5"/>
@@ -1491,7 +1531,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6"/>
@@ -1510,7 +1550,7 @@
       <c r="H12" s="16"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1764,7 +1804,7 @@
       <c r="C8" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2045,7 +2085,7 @@
       <c r="J18" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2057,7 +2097,8 @@
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="17.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.375" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.375" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.375" style="2" customWidth="1"/>
     <col min="8" max="8" width="18.5" style="2" bestFit="1" customWidth="1"/>
@@ -2068,10 +2109,10 @@
   <sheetData>
     <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -2088,34 +2129,34 @@
         <v>40</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="F2" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -2127,13 +2168,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>45</v>
@@ -2162,14 +2203,14 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -2194,14 +2235,14 @@
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="G5" s="2">
         <v>3</v>
@@ -2226,14 +2267,14 @@
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -2263,7 +2304,7 @@
       <c r="J12" s="16"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2290,7 +2331,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -2309,19 +2350,19 @@
         <v>40</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -2335,19 +2376,19 @@
         <v>1</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
@@ -2357,7 +2398,7 @@
         <v>10001</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2">
         <v>10001</v>
@@ -2378,7 +2419,7 @@
         <v>10002</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D5" s="2">
         <v>10002</v>
@@ -2399,7 +2440,7 @@
         <v>10003</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D6" s="2">
         <v>10003</v>
@@ -2420,7 +2461,7 @@
         <v>10004</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D7" s="16">
         <v>50001</v>
@@ -2447,7 +2488,7 @@
       <c r="E18" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2470,7 +2511,7 @@
   <sheetData>
     <row r="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>44</v>
@@ -2489,31 +2530,31 @@
         <v>40</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>59</v>
-      </c>
       <c r="H2" s="9" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="J2" s="23" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -2525,10 +2566,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>53</v>
+        <v>152</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>45</v>
@@ -2557,11 +2598,11 @@
         <v>10001</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -2570,7 +2611,7 @@
         <v>10001</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="K4">
         <v>2001</v>
@@ -2582,11 +2623,11 @@
         <v>10002</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -2595,7 +2636,7 @@
         <v>10001</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="K5">
         <v>2001</v>
@@ -2607,11 +2648,11 @@
         <v>10003</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -2620,7 +2661,7 @@
         <v>10001</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="K6">
         <v>2001</v>
@@ -2632,11 +2673,11 @@
         <v>20001</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="2" t="s">
-        <v>48</v>
+        <v>147</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
@@ -2660,11 +2701,11 @@
         <v>20002</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
@@ -2688,11 +2729,11 @@
         <v>20003</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F9" s="2">
         <v>1</v>
@@ -2716,11 +2757,11 @@
         <v>30001</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="F10">
         <v>30</v>
@@ -2744,11 +2785,11 @@
         <v>30002</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F11">
         <v>30</v>
@@ -2772,11 +2813,11 @@
         <v>30003</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F12">
         <v>30</v>
@@ -2800,18 +2841,18 @@
         <v>40001</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>149</v>
       </c>
       <c r="F13"/>
       <c r="H13" s="2">
         <v>10001</v>
       </c>
       <c r="J13" s="25" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="K13">
         <v>1001</v>
@@ -2823,18 +2864,18 @@
         <v>40002</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F14"/>
       <c r="H14" s="2">
         <v>10001</v>
       </c>
       <c r="J14" s="25" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="K14">
         <v>1001</v>
@@ -2846,18 +2887,18 @@
         <v>40003</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F15"/>
       <c r="H15" s="2">
         <v>10001</v>
       </c>
       <c r="J15" s="25" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="K15">
         <v>1001</v>
@@ -2869,11 +2910,11 @@
         <v>50001</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -2959,7 +3000,7 @@
       <c r="J28" s="27"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -2985,8 +3026,8 @@
       <c r="A1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>46</v>
+      <c r="B1" s="28" t="s">
+        <v>155</v>
       </c>
       <c r="C1" s="10"/>
     </row>
@@ -2999,7 +3040,7 @@
         <v>40</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>6</v>
+        <v>157</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>7</v>
@@ -3031,13 +3072,13 @@
         <v>10001</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -3107,7 +3148,7 @@
       <c r="C20" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3115,51 +3156,57 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.375" customWidth="1"/>
-    <col min="4" max="6" width="17.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="18.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.875" style="2" customWidth="1"/>
+    <col min="6" max="7" width="17.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="18.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>131</v>
+        <v>55</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>158</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G1" s="10"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="2" t="s">
         <v>45</v>
@@ -3171,16 +3218,19 @@
         <v>45</v>
       </c>
       <c r="E3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>56</v>
-      </c>
       <c r="G3" s="9" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>1</v>
       </c>
@@ -3190,15 +3240,16 @@
       <c r="D4">
         <v>10001</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4">
         <v>30</v>
       </c>
-      <c r="F4" t="s">
-        <v>138</v>
-      </c>
       <c r="G4"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>2</v>
       </c>
@@ -3208,15 +3259,16 @@
       <c r="D5">
         <v>10002</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="2">
         <v>15</v>
       </c>
-      <c r="F5" t="s">
-        <v>138</v>
-      </c>
       <c r="G5"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>3</v>
       </c>
@@ -3226,15 +3278,16 @@
       <c r="D6">
         <v>10001</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6">
         <v>40</v>
       </c>
-      <c r="F6" t="s">
-        <v>138</v>
-      </c>
       <c r="G6"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>4</v>
       </c>
@@ -3244,14 +3297,15 @@
       <c r="D7">
         <v>10002</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="2">
         <v>20</v>
       </c>
-      <c r="F7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G7"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>5</v>
       </c>
@@ -3261,14 +3315,15 @@
       <c r="D8">
         <v>10003</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" t="s">
+        <v>125</v>
+      </c>
+      <c r="F8" s="2">
         <v>10</v>
       </c>
-      <c r="F8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G8"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>6</v>
       </c>
@@ -3278,17 +3333,17 @@
       <c r="D9">
         <v>10001</v>
       </c>
-      <c r="E9" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F9" t="s">
-        <v>138</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>125</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>7</v>
       </c>
@@ -3298,17 +3353,17 @@
       <c r="D10">
         <v>10002</v>
       </c>
-      <c r="E10" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F10" t="s">
-        <v>138</v>
-      </c>
-      <c r="G10" s="2">
+      <c r="E10" t="s">
+        <v>125</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>8</v>
       </c>
@@ -3318,17 +3373,17 @@
       <c r="D11">
         <v>10003</v>
       </c>
-      <c r="E11" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F11" t="s">
-        <v>138</v>
-      </c>
-      <c r="G11" s="2">
+      <c r="E11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>9</v>
       </c>
@@ -3338,17 +3393,17 @@
       <c r="D12" s="2">
         <v>20001</v>
       </c>
-      <c r="E12" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F12" t="s">
-        <v>138</v>
-      </c>
-      <c r="G12" s="2">
+      <c r="E12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>10</v>
       </c>
@@ -3358,17 +3413,17 @@
       <c r="D13">
         <v>10001</v>
       </c>
-      <c r="E13" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F13" t="s">
-        <v>138</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E13" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>11</v>
       </c>
@@ -3378,17 +3433,17 @@
       <c r="D14">
         <v>10002</v>
       </c>
-      <c r="E14" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G14" s="2">
+      <c r="E14" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>12</v>
       </c>
@@ -3398,17 +3453,17 @@
       <c r="D15">
         <v>10003</v>
       </c>
-      <c r="E15" s="2">
-        <v>9999</v>
-      </c>
-      <c r="F15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G15" s="2">
+      <c r="E15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>13</v>
       </c>
@@ -3418,14 +3473,15 @@
       <c r="D16">
         <v>10001</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" t="s">
+        <v>125</v>
+      </c>
+      <c r="F16" s="2">
         <v>50</v>
       </c>
-      <c r="F16" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G16"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>14</v>
       </c>
@@ -3435,14 +3491,15 @@
       <c r="D17">
         <v>10001</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="2">
         <v>50</v>
       </c>
-      <c r="F17" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G17"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>15</v>
       </c>
@@ -3452,14 +3509,15 @@
       <c r="D18">
         <v>10001</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" t="s">
+        <v>127</v>
+      </c>
+      <c r="F18" s="2">
         <v>50</v>
       </c>
-      <c r="F18" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G18"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>16</v>
       </c>
@@ -3467,29 +3525,29 @@
         <v>50001</v>
       </c>
       <c r="D19" s="2">
-        <v>50001</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+        <v>30001</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3512,10 +3570,10 @@
   <sheetData>
     <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -3534,25 +3592,25 @@
         <v>40</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -3564,19 +3622,19 @@
         <v>1</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>45</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I3" s="9" t="s">
         <v>45</v>
@@ -3590,19 +3648,19 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E4">
         <v>1001</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H4" s="2">
         <v>5</v>
@@ -3619,19 +3677,19 @@
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E5">
         <v>1001</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H5" s="2">
         <v>15</v>
@@ -3648,19 +3706,19 @@
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E6">
         <v>1001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H6" s="2">
         <v>100</v>
@@ -3677,19 +3735,19 @@
         <v>4</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E7">
         <v>1001</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H7" s="2">
         <v>5</v>
@@ -3706,19 +3764,19 @@
         <v>5</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E8">
         <v>1001</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H8" s="2">
         <v>15</v>
@@ -3735,19 +3793,19 @@
         <v>6</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E9">
         <v>1001</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H9" s="2">
         <v>100</v>
@@ -3764,19 +3822,19 @@
         <v>7</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E10">
         <v>1001</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H10" s="2">
         <v>100</v>
@@ -3793,19 +3851,19 @@
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E11">
         <v>1001</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H11" s="2">
         <v>100</v>
@@ -3822,19 +3880,19 @@
         <v>9</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E12">
         <v>1001</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="H12" s="2">
         <v>100</v>
@@ -3851,19 +3909,19 @@
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E13">
         <v>1001</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -3880,19 +3938,19 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E14">
         <v>1001</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H14" s="2">
         <v>15</v>
@@ -3909,19 +3967,19 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E15">
         <v>1001</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H15" s="2">
         <v>100</v>
@@ -3938,19 +3996,19 @@
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E16">
         <v>2001</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H16" s="2">
         <v>2.5</v>
@@ -3967,19 +4025,19 @@
         <v>14</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E17">
         <v>2001</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H17" s="2">
         <v>7.5</v>
@@ -3996,19 +4054,19 @@
         <v>15</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E18">
         <v>2001</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H18" s="2">
         <v>100</v>
@@ -4025,19 +4083,19 @@
         <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E19">
         <v>2001</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H19" s="2">
         <v>2.5</v>
@@ -4054,19 +4112,19 @@
         <v>17</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E20">
         <v>2001</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H20" s="2">
         <v>7.5</v>
@@ -4083,19 +4141,19 @@
         <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E21">
         <v>2001</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H21" s="2">
         <v>100</v>
@@ -4112,19 +4170,19 @@
         <v>19</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E22">
         <v>2001</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H22" s="2">
         <v>100</v>
@@ -4141,19 +4199,19 @@
         <v>20</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E23">
         <v>2001</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H23" s="2">
         <v>100</v>
@@ -4170,19 +4228,19 @@
         <v>21</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E24">
         <v>2001</v>
       </c>
       <c r="F24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="H24" s="2">
         <v>100</v>
@@ -4199,19 +4257,19 @@
         <v>22</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E25">
         <v>2001</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H25" s="2">
         <v>0.5</v>
@@ -4228,19 +4286,19 @@
         <v>23</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E26">
         <v>2001</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H26" s="2">
         <v>7.5</v>
@@ -4257,19 +4315,19 @@
         <v>24</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E27">
         <v>2001</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H27" s="2">
         <v>100</v>
@@ -4286,19 +4344,19 @@
         <v>25</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E28">
         <v>3001</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H28" s="2">
         <v>100</v>
@@ -4315,19 +4373,19 @@
         <v>26</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E29">
         <v>3001</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H29" s="2">
         <v>100</v>
@@ -4344,19 +4402,19 @@
         <v>27</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E30">
         <v>3001</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="H30" s="2">
         <v>100</v>
@@ -4373,19 +4431,19 @@
         <v>28</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E31">
         <v>3001</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H31" s="2">
         <v>100</v>
@@ -4402,19 +4460,19 @@
         <v>29</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E32">
         <v>3001</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H32" s="2">
         <v>100</v>
@@ -4431,19 +4489,19 @@
         <v>30</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E33">
         <v>3001</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H33" s="2">
         <v>100</v>
@@ -4460,19 +4518,19 @@
         <v>31</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E34">
         <v>3001</v>
       </c>
       <c r="F34" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="H34" s="2">
         <v>100</v>
@@ -4489,19 +4547,19 @@
         <v>32</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E35">
         <v>3001</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="H35" s="2">
         <v>100</v>
@@ -4514,7 +4572,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,19 +4,17 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="7"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
-    <sheet name="#MapInfo" sheetId="13" r:id="rId2"/>
-    <sheet name="#MonsterSpawnInfo" sheetId="14" r:id="rId3"/>
-    <sheet name="#Dungeon" sheetId="18" r:id="rId4"/>
-    <sheet name="#StageGroup" sheetId="16" r:id="rId5"/>
-    <sheet name="#Stage" sheetId="17" r:id="rId6"/>
-    <sheet name="#MapData" sheetId="15" r:id="rId7"/>
-    <sheet name="#MonsterSpawn" sheetId="21" r:id="rId8"/>
-    <sheet name="#DropObject" sheetId="19" r:id="rId9"/>
-    <sheet name="#StageReward" sheetId="20" r:id="rId10"/>
+    <sheet name="#Dungeon" sheetId="18" r:id="rId2"/>
+    <sheet name="#StageGroup" sheetId="16" r:id="rId3"/>
+    <sheet name="#Stage" sheetId="17" r:id="rId4"/>
+    <sheet name="#MapData" sheetId="15" r:id="rId5"/>
+    <sheet name="#MonsterSpawn" sheetId="21" r:id="rId6"/>
+    <sheet name="#DropObject" sheetId="19" r:id="rId7"/>
+    <sheet name="#StageReward" sheetId="20" r:id="rId8"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -68,50 +66,38 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="140">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>초원</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BGM</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sound_Map_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>빙하</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>용암</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Sound_Map_2</t>
@@ -123,164 +109,56 @@
     <t>Prefab_GridMap_01</t>
   </si>
   <si>
-    <t>BattleType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wave</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Raid</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <t>Name</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>지옥</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterSpawnInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterID_01</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnInfo_01</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnInfo_02</t>
-  </si>
-  <si>
-    <t>SpawnInfo_03</t>
-  </si>
-  <si>
-    <t>SpawnInfo_04</t>
-  </si>
-  <si>
-    <t>SpawnInfo_05</t>
-  </si>
-  <si>
-    <t>!BattleType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnCount</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterID_02</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterID_03</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalCount_01</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterCount_01</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalTime_01</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterCount_02</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalCount_02</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalTime_02</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterCount_03</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalCount_03</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>IntervalTime_03</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClearRewardIDs</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001;10002;20001;20002;30001;40001</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>지옥</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stage</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>MapModeType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BuildingDestroy</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Defense</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Capture</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Breakthrough</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BossBattle</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>LimitTime</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -297,15 +175,15 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>초원</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StageGroup</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -321,15 +199,15 @@
       </rPr>
       <t>int</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StageID_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StageID_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StageID_3</t>
@@ -342,11 +220,11 @@
   </si>
   <si>
     <t>StageGroupID_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StageGroupID_3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StageGroupID_4</t>
@@ -356,19 +234,19 @@
   </si>
   <si>
     <t>건물 파괴 1-1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>디펜스 1-1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>디펜스 1-2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>디펜스 1-3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>건물 파괴 1-2</t>
@@ -378,47 +256,47 @@
   </si>
   <si>
     <t>점령 1-1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>점령 1-2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>점령 1-3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>돌파 1-1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>돌파 1-2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>돌파 1-3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>보스전 1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>MapObjectIDs</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>던전1의  스테이지1 그룹</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>던전1의  스테이지2 그룹</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>던전1의  스테이지3 그룹</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -434,317 +312,342 @@
       </rPr>
       <t xml:space="preserve"> 추가 스테이지 그룹</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>HealOrb</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StaminaOrb</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StageReward</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>DropObject</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>StageRewardIDs</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>체력 회복 구슬</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>스태미너 회복 구슬</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>MagicEssence</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>ArcaneScroll</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>비전 주문서</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>마력정수</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>MonsterType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!MonsterTypes</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Elite</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Boss</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>DropChance</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>MinCount</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>MaxCount</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>카드 구매창이 뜨게 하는 스크롤</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>체력을 25% 회복시키는 오브</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>스태미너를 25% 회복 시키는 오브</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>카드구매용 임시재화</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>적 웨이브가 n번 오고 모두 섬멸</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>지정된 공간에서 n초 동안 버티면 승리</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>적 저자선을 뚫고 지정된 위치로 이동하면 승리</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>보스를 n마리 죽이면 승리</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>지정된 건물을 n개 파괴하면 승리</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>체력 25% 회복</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>스태미너 25% 회복</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>스킬 구매 재화</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>스킬 구매 목록</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>GroupID</t>
   </si>
   <si>
     <t>GroupID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001;10002</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnPoint_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnPoint_02</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnPoint_03</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>40001;40002;40003</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropObjectType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!DropObjectType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecommandedLvText</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 ~ 5</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>5 ~ 10</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>10 ~ 15</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dungeon</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Image_Stage_1</t>
+  </si>
+  <si>
+    <t>Image_Stage_2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 고블린 숲(쉬움)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 고블린 숲(보통)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 고블린 숲(어려움)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExtraStageGroupID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ModeType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingDestroy</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Capture</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Breakthrough</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossBattle</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClearValue</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!MapModeType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpawnGroupIDs</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapData</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound_Map_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpawn</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnPoint</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnStepCount</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnAllCount</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpawnStepDelay</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>TotalStageCount</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageGroupID_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropObjectType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab_DropItem_ArcaneScroll</t>
+  </si>
+  <si>
+    <t>Prefab_DropItem_HealOrb</t>
+  </si>
+  <si>
+    <t>Prefab_DropItem_StaminaOrb</t>
+  </si>
+  <si>
+    <t>Path</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab_DropItem_MagicEssence</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>DropObjectGroupID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001;10002</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnPoint_01</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnPoint_02</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnPoint_03</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>40001;40002;40003</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DropObjectType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!DropObjectType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>RecommandedLvText</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 ~ 5</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>5 ~ 10</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>10 ~ 15</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Image_Stage_1</t>
-  </si>
-  <si>
-    <t>Image_Stage_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 고블린 숲(쉬움)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>2. 고블린 숲(보통)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. 고블린 숲(어려움)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>TotalStageCount</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StageGroupID_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExtraStageGroupID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ModeType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuildingDestroy</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Capture</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Breakthrough</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BossBattle</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClearValue</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!MapModeType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterSpawnGroupIDs</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapData</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sound_Map_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterSpawn</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnPoint</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnStepCount</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnAllCount</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpawnStepDelay</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -754,20 +657,12 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -951,12 +846,12 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -970,50 +865,46 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -1025,7 +916,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1308,7 +1199,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1316,7 +1207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="1" bestFit="1" customWidth="1"/>
@@ -1332,765 +1223,98 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>14</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="D1" s="17"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
-        <v>15</v>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="19"/>
+      <c r="D3" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>111</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="17"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>112</v>
+      <c r="B9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D12" s="19"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>106</v>
+      <c r="B10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="17.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="18.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" s="11"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4" s="16"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="2">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="11"/>
-      <c r="F5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5" s="16"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="2">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6" s="16"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H10" s="16"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H12" s="16"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="17.625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="35.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.75" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="18.5" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="10"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2">
-        <v>3</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2">
-        <v>2</v>
-      </c>
-      <c r="J4" s="2">
-        <v>3</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B5" s="2">
-        <v>2</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="2">
-        <v>5</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2">
-        <v>2</v>
-      </c>
-      <c r="K5" s="2">
-        <v>3</v>
-      </c>
-      <c r="L5" s="2">
-        <v>4</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B6" s="2">
-        <v>3</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="2">
-        <v>5</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2">
-        <v>2</v>
-      </c>
-      <c r="K6" s="2">
-        <v>3</v>
-      </c>
-      <c r="L6" s="2">
-        <v>4</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B7" s="2">
-        <v>4</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C8" s="11"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S18"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5" style="2" customWidth="1"/>
-    <col min="17" max="17" width="20.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.5" style="2" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>10001</v>
-      </c>
-      <c r="D4" s="2">
-        <v>30</v>
-      </c>
-      <c r="G4"/>
-      <c r="K4"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B5" s="2">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>10001</v>
-      </c>
-      <c r="D5" s="2">
-        <v>30</v>
-      </c>
-      <c r="G5">
-        <v>10002</v>
-      </c>
-      <c r="H5" s="2">
-        <v>10</v>
-      </c>
-      <c r="K5"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B6" s="2">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>10001</v>
-      </c>
-      <c r="D6" s="2">
-        <v>30</v>
-      </c>
-      <c r="G6">
-        <v>10002</v>
-      </c>
-      <c r="H6" s="2">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>10003</v>
-      </c>
-      <c r="L6" s="2">
-        <v>1</v>
-      </c>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B7" s="2">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>10001</v>
-      </c>
-      <c r="D7" s="2">
-        <v>30</v>
-      </c>
-      <c r="G7" s="5">
-        <v>30001</v>
-      </c>
-      <c r="H7" s="2">
-        <v>10</v>
-      </c>
-      <c r="K7">
-        <v>10003</v>
-      </c>
-      <c r="L7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B8" s="2">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2">
-        <v>100001</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G14"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G15"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-    </row>
-    <row r="17" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G17"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-    </row>
-    <row r="18" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2108,11 +1332,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>136</v>
+      <c r="A1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -2126,76 +1350,76 @@
         <v>2</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="2" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -2203,14 +1427,14 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -2226,7 +1450,7 @@
       </c>
       <c r="K4"/>
       <c r="L4"/>
-      <c r="M4" s="16">
+      <c r="M4" s="14">
         <v>10004</v>
       </c>
     </row>
@@ -2235,14 +1459,14 @@
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="G5" s="2">
         <v>3</v>
@@ -2258,7 +1482,7 @@
       </c>
       <c r="K5"/>
       <c r="L5"/>
-      <c r="M5" s="16">
+      <c r="M5" s="14">
         <v>10004</v>
       </c>
     </row>
@@ -2267,14 +1491,14 @@
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -2290,35 +1514,35 @@
       </c>
       <c r="K6"/>
       <c r="L6"/>
-      <c r="M6" s="16">
+      <c r="M6" s="14">
         <v>10004</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="J10" s="16"/>
+      <c r="J10" s="14"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="J11" s="16"/>
+      <c r="J11" s="14"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="J12" s="16"/>
+      <c r="J12" s="14"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.75" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.625" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="17.375" style="16" customWidth="1"/>
-    <col min="8" max="8" width="24" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.625" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="17.375" style="14" customWidth="1"/>
+    <col min="8" max="8" width="24" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.375" style="2" customWidth="1"/>
     <col min="10" max="10" width="17.5" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.625" style="2" customWidth="1"/>
@@ -2327,11 +1551,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>57</v>
+      <c r="B1" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -2343,62 +1567,62 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>63</v>
+      <c r="C2" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>32</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>58</v>
+      <c r="C3" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>27</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="16">
+      <c r="B4" s="14">
         <v>10001</v>
       </c>
-      <c r="C4" s="17" t="s">
-        <v>82</v>
+      <c r="C4" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="D4" s="2">
         <v>10001</v>
@@ -2412,14 +1636,14 @@
       <c r="G4" s="2">
         <v>40001</v>
       </c>
-      <c r="H4" s="17"/>
+      <c r="H4" s="15"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="16">
+      <c r="B5" s="14">
         <v>10002</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>83</v>
+      <c r="C5" s="15" t="s">
+        <v>52</v>
       </c>
       <c r="D5" s="2">
         <v>10002</v>
@@ -2433,14 +1657,14 @@
       <c r="G5" s="2">
         <v>40002</v>
       </c>
-      <c r="H5" s="17"/>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="16">
+      <c r="B6" s="14">
         <v>10003</v>
       </c>
-      <c r="C6" s="17" t="s">
-        <v>84</v>
+      <c r="C6" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="D6" s="2">
         <v>10003</v>
@@ -2457,13 +1681,13 @@
       <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="16">
+      <c r="B7" s="14">
         <v>10004</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" s="16">
+      <c r="C7" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="14">
         <v>50001</v>
       </c>
       <c r="I7" s="11"/>
@@ -2488,12 +1712,12 @@
       <c r="E18" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2503,23 +1727,23 @@
     <col min="3" max="5" width="17.375" style="2" customWidth="1"/>
     <col min="6" max="8" width="15.5" style="2" customWidth="1"/>
     <col min="9" max="9" width="19.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.5" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.5" style="23" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.25" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>44</v>
+      <c r="A1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
-      <c r="J1" s="22"/>
+      <c r="J1" s="20"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
@@ -2527,70 +1751,70 @@
         <v>2</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J2" s="23" t="s">
-        <v>154</v>
+        <v>50</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>120</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="2" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3" s="23" t="s">
-        <v>45</v>
+        <v>14</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>14</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -2598,11 +1822,11 @@
         <v>10001</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -2610,8 +1834,8 @@
       <c r="H4" s="2">
         <v>10001</v>
       </c>
-      <c r="J4" s="24" t="s">
-        <v>122</v>
+      <c r="J4" s="22" t="s">
+        <v>90</v>
       </c>
       <c r="K4">
         <v>2001</v>
@@ -2623,11 +1847,11 @@
         <v>10002</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -2635,8 +1859,8 @@
       <c r="H5" s="2">
         <v>10001</v>
       </c>
-      <c r="J5" s="24" t="s">
-        <v>122</v>
+      <c r="J5" s="22" t="s">
+        <v>90</v>
       </c>
       <c r="K5">
         <v>2001</v>
@@ -2648,11 +1872,11 @@
         <v>10003</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -2660,8 +1884,8 @@
       <c r="H6" s="2">
         <v>10001</v>
       </c>
-      <c r="J6" s="24" t="s">
-        <v>122</v>
+      <c r="J6" s="22" t="s">
+        <v>90</v>
       </c>
       <c r="K6">
         <v>2001</v>
@@ -2673,11 +1897,11 @@
         <v>20001</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="2" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
@@ -2688,7 +1912,7 @@
       <c r="H7" s="2">
         <v>10001</v>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="22">
         <v>20001</v>
       </c>
       <c r="K7">
@@ -2701,11 +1925,11 @@
         <v>20002</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
@@ -2716,7 +1940,7 @@
       <c r="H8" s="2">
         <v>10001</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="22">
         <v>20001</v>
       </c>
       <c r="K8">
@@ -2729,11 +1953,11 @@
         <v>20003</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="F9" s="2">
         <v>1</v>
@@ -2744,7 +1968,7 @@
       <c r="H9" s="2">
         <v>10001</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="22">
         <v>20001</v>
       </c>
       <c r="K9">
@@ -2757,11 +1981,11 @@
         <v>30001</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="F10">
         <v>30</v>
@@ -2772,7 +1996,7 @@
       <c r="H10" s="2">
         <v>10001</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="23">
         <v>30001</v>
       </c>
       <c r="K10">
@@ -2785,11 +2009,11 @@
         <v>30002</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="F11">
         <v>30</v>
@@ -2800,7 +2024,7 @@
       <c r="H11" s="2">
         <v>10001</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="23">
         <v>30001</v>
       </c>
       <c r="K11">
@@ -2813,11 +2037,11 @@
         <v>30003</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="F12">
         <v>30</v>
@@ -2828,7 +2052,7 @@
       <c r="H12" s="2">
         <v>10001</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="23">
         <v>30001</v>
       </c>
       <c r="K12">
@@ -2841,18 +2065,18 @@
         <v>40001</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="F13"/>
       <c r="H13" s="2">
         <v>10001</v>
       </c>
-      <c r="J13" s="25" t="s">
-        <v>128</v>
+      <c r="J13" s="23" t="s">
+        <v>96</v>
       </c>
       <c r="K13">
         <v>1001</v>
@@ -2864,18 +2088,18 @@
         <v>40002</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="F14"/>
       <c r="H14" s="2">
         <v>10001</v>
       </c>
-      <c r="J14" s="25" t="s">
-        <v>128</v>
+      <c r="J14" s="23" t="s">
+        <v>96</v>
       </c>
       <c r="K14">
         <v>1001</v>
@@ -2887,18 +2111,18 @@
         <v>40003</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="F15"/>
       <c r="H15" s="2">
         <v>10001</v>
       </c>
-      <c r="J15" s="25" t="s">
-        <v>128</v>
+      <c r="J15" s="23" t="s">
+        <v>96</v>
       </c>
       <c r="K15">
         <v>1001</v>
@@ -2910,11 +2134,11 @@
         <v>50001</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" t="s">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -2922,7 +2146,7 @@
       <c r="H16" s="2">
         <v>10001</v>
       </c>
-      <c r="J16" s="26">
+      <c r="J16" s="24">
         <v>50001</v>
       </c>
       <c r="K16">
@@ -2948,7 +2172,7 @@
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.3">
       <c r="I20"/>
-      <c r="J20" s="27"/>
+      <c r="J20" s="25"/>
       <c r="K20"/>
       <c r="L20"/>
     </row>
@@ -2957,13 +2181,13 @@
       <c r="E21" s="11"/>
       <c r="F21"/>
       <c r="I21"/>
-      <c r="J21" s="27"/>
+      <c r="J21" s="25"/>
       <c r="K21"/>
       <c r="L21"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.3">
       <c r="I22"/>
-      <c r="J22" s="27"/>
+      <c r="J22" s="25"/>
       <c r="K22"/>
       <c r="L22"/>
     </row>
@@ -2973,13 +2197,13 @@
       <c r="E23" s="11"/>
       <c r="F23"/>
       <c r="I23"/>
-      <c r="J23" s="27"/>
+      <c r="J23" s="25"/>
       <c r="K23"/>
       <c r="L23"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.3">
       <c r="I24" s="5"/>
-      <c r="J24" s="27"/>
+      <c r="J24" s="25"/>
       <c r="K24"/>
       <c r="L24"/>
     </row>
@@ -2988,25 +2212,25 @@
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25"/>
-      <c r="J25" s="27"/>
+      <c r="J25" s="25"/>
     </row>
     <row r="26" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="J26" s="27"/>
+      <c r="J26" s="25"/>
     </row>
     <row r="27" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="J27" s="27"/>
+      <c r="J27" s="25"/>
     </row>
     <row r="28" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="J28" s="27"/>
+      <c r="J28" s="25"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3023,11 +2247,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="28" t="s">
-        <v>155</v>
+      <c r="B1" s="26" t="s">
+        <v>121</v>
       </c>
       <c r="C1" s="10"/>
     </row>
@@ -3037,13 +2261,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -3072,13 +2296,13 @@
         <v>10001</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -3086,13 +2310,13 @@
         <v>20001</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -3100,13 +2324,13 @@
         <v>30001</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -3114,13 +2338,13 @@
         <v>40001</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -3148,13 +2372,13 @@
       <c r="C20" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3170,11 +2394,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>158</v>
+      <c r="A1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>124</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -3188,46 +2412,46 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="2" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -3241,7 +2465,7 @@
         <v>10001</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="F4">
         <v>30</v>
@@ -3260,7 +2484,7 @@
         <v>10002</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="F5" s="2">
         <v>15</v>
@@ -3279,7 +2503,7 @@
         <v>10001</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="F6">
         <v>40</v>
@@ -3298,7 +2522,7 @@
         <v>10002</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="F7" s="2">
         <v>20</v>
@@ -3316,7 +2540,7 @@
         <v>10003</v>
       </c>
       <c r="E8" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="F8" s="2">
         <v>10</v>
@@ -3334,7 +2558,7 @@
         <v>10001</v>
       </c>
       <c r="E9" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -3354,7 +2578,7 @@
         <v>10002</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -3374,7 +2598,7 @@
         <v>10003</v>
       </c>
       <c r="E11" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -3394,7 +2618,7 @@
         <v>20001</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -3414,7 +2638,7 @@
         <v>10001</v>
       </c>
       <c r="E13" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -3434,7 +2658,7 @@
         <v>10002</v>
       </c>
       <c r="E14" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -3454,7 +2678,7 @@
         <v>10003</v>
       </c>
       <c r="E15" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -3474,7 +2698,7 @@
         <v>10001</v>
       </c>
       <c r="E16" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="F16" s="2">
         <v>50</v>
@@ -3492,7 +2716,7 @@
         <v>10001</v>
       </c>
       <c r="E17" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="F17" s="2">
         <v>50</v>
@@ -3510,7 +2734,7 @@
         <v>10001</v>
       </c>
       <c r="E18" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="F18" s="2">
         <v>50</v>
@@ -3528,7 +2752,7 @@
         <v>30001</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
@@ -3547,14 +2771,14 @@
       <c r="B23"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
@@ -3563,368 +2787,403 @@
     <col min="4" max="4" width="25.125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="17.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="17.375" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="29.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="17.375" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>89</v>
+    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="G1" s="10"/>
       <c r="I1" s="10"/>
       <c r="J1" s="10"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="10"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>102</v>
+      <c r="G2" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="2" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G3" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>105</v>
+      <c r="G3" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E4">
         <v>1001</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H4" s="2">
+        <v>135</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="2">
         <v>5</v>
       </c>
-      <c r="I4" s="2">
-        <v>1</v>
-      </c>
       <c r="J4" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E5">
         <v>1001</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H5" s="2">
+        <v>135</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="2">
         <v>15</v>
       </c>
-      <c r="I5" s="2">
-        <v>1</v>
-      </c>
       <c r="J5" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E6">
         <v>1001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H6" s="2">
+        <v>135</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" s="2">
         <v>100</v>
       </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
       <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>4</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="E7">
         <v>1001</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H7" s="2">
+        <v>136</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" s="2">
         <v>5</v>
       </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
       <c r="J7" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>5</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="E8">
         <v>1001</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H8" s="2">
+        <v>136</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="2">
         <v>15</v>
       </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
       <c r="J8" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>6</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="E9">
         <v>1001</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H9" s="2">
+        <v>136</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="2">
         <v>100</v>
       </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
       <c r="J9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>7</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="E10">
         <v>1001</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H10" s="2">
+        <v>138</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" s="2">
         <v>100</v>
       </c>
-      <c r="I10" s="2">
+      <c r="J10" s="2">
         <v>10</v>
       </c>
-      <c r="J10" s="2">
+      <c r="K10" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="E11">
         <v>1001</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" s="2">
         <v>100</v>
       </c>
-      <c r="H11" s="2">
+      <c r="J11" s="2">
+        <v>50</v>
+      </c>
+      <c r="K11" s="2">
         <v>100</v>
       </c>
-      <c r="I11" s="2">
-        <v>50</v>
-      </c>
-      <c r="J11" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>9</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="E12">
         <v>1001</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H12" s="2">
+        <v>138</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12" s="2">
         <v>100</v>
       </c>
-      <c r="I12" s="2">
+      <c r="J12" s="2">
         <v>300</v>
       </c>
-      <c r="J12" s="2">
+      <c r="K12" s="2">
         <v>500</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="E13">
         <v>1001</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="I13" s="2">
         <v>1</v>
@@ -3932,647 +3191,830 @@
       <c r="J13" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="E14">
         <v>1001</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H14" s="2">
+        <v>134</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="2">
         <v>15</v>
       </c>
-      <c r="I14" s="2">
-        <v>1</v>
-      </c>
       <c r="J14" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="E15">
         <v>1001</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H15" s="2">
+        <v>134</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I15" s="2">
         <v>100</v>
       </c>
-      <c r="I15" s="2">
-        <v>1</v>
-      </c>
       <c r="J15" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E16">
         <v>2001</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H16" s="2">
+        <v>135</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I16" s="2">
         <v>2.5</v>
       </c>
-      <c r="I16" s="2">
-        <v>1</v>
-      </c>
       <c r="J16" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>14</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E17">
         <v>2001</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H17" s="2">
+        <v>135</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" s="2">
         <v>7.5</v>
       </c>
-      <c r="I17" s="2">
-        <v>1</v>
-      </c>
       <c r="J17" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>15</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E18">
         <v>2001</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H18" s="2">
+        <v>135</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I18" s="2">
         <v>100</v>
       </c>
-      <c r="I18" s="2">
-        <v>1</v>
-      </c>
       <c r="J18" s="2">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="E19">
         <v>2001</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H19" s="2">
+        <v>136</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I19" s="2">
         <v>2.5</v>
       </c>
-      <c r="I19" s="2">
-        <v>1</v>
-      </c>
       <c r="J19" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>17</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="E20">
         <v>2001</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H20" s="2">
+        <v>136</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="2">
         <v>7.5</v>
       </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
       <c r="J20" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="E21">
         <v>2001</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H21" s="2">
+        <v>136</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I21" s="2">
         <v>100</v>
       </c>
-      <c r="I21" s="2">
-        <v>1</v>
-      </c>
       <c r="J21" s="2">
+        <v>1</v>
+      </c>
+      <c r="K21" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>19</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="E22">
         <v>2001</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H22" s="2">
+        <v>138</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" s="2">
         <v>100</v>
       </c>
-      <c r="I22" s="2">
+      <c r="J22" s="2">
         <v>5</v>
       </c>
-      <c r="J22" s="2">
+      <c r="K22" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>20</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="E23">
         <v>2001</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="G23" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I23" s="2">
         <v>100</v>
       </c>
-      <c r="H23" s="2">
-        <v>100</v>
-      </c>
-      <c r="I23" s="2">
+      <c r="J23" s="2">
         <v>25</v>
       </c>
-      <c r="J23" s="2">
+      <c r="K23" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <v>21</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="E24">
         <v>2001</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H24" s="2">
+        <v>138</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I24" s="2">
         <v>100</v>
       </c>
-      <c r="I24" s="2">
+      <c r="J24" s="2">
         <v>300</v>
       </c>
-      <c r="J24" s="2">
+      <c r="K24" s="2">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <v>22</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="E25">
         <v>2001</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H25" s="2">
+        <v>134</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I25" s="2">
         <v>0.5</v>
       </c>
-      <c r="I25" s="2">
-        <v>1</v>
-      </c>
       <c r="J25" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K25" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <v>23</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="E26">
         <v>2001</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H26" s="2">
+        <v>134</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I26" s="2">
         <v>7.5</v>
       </c>
-      <c r="I26" s="2">
-        <v>1</v>
-      </c>
       <c r="J26" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <v>24</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="E27">
         <v>2001</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H27" s="2">
+        <v>134</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I27" s="2">
         <v>100</v>
       </c>
-      <c r="I27" s="2">
-        <v>1</v>
-      </c>
       <c r="J27" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K27" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <v>25</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E28">
         <v>3001</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H28" s="2">
+        <v>135</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I28" s="2">
         <v>100</v>
       </c>
-      <c r="I28" s="2">
-        <v>1</v>
-      </c>
       <c r="J28" s="2">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <v>26</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="E29">
         <v>3001</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H29" s="2">
+        <v>136</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I29" s="2">
         <v>100</v>
       </c>
-      <c r="I29" s="2">
-        <v>1</v>
-      </c>
       <c r="J29" s="2">
+        <v>1</v>
+      </c>
+      <c r="K29" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <v>27</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="E30">
         <v>3001</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H30" s="2">
+        <v>138</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I30" s="2">
         <v>100</v>
       </c>
-      <c r="I30" s="2">
+      <c r="J30" s="2">
         <v>300</v>
       </c>
-      <c r="J30" s="2">
+      <c r="K30" s="2">
         <v>500</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <v>28</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="E31">
         <v>3001</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H31" s="2">
+        <v>134</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I31" s="2">
         <v>100</v>
       </c>
-      <c r="I31" s="2">
-        <v>1</v>
-      </c>
       <c r="J31" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K31" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
         <v>29</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E32">
         <v>3001</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H32" s="2">
+        <v>135</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I32" s="2">
         <v>100</v>
       </c>
-      <c r="I32" s="2">
-        <v>1</v>
-      </c>
       <c r="J32" s="2">
+        <v>1</v>
+      </c>
+      <c r="K32" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="2">
         <v>30</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="E33">
         <v>3001</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H33" s="2">
+        <v>136</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I33" s="2">
         <v>100</v>
       </c>
-      <c r="I33" s="2">
-        <v>1</v>
-      </c>
       <c r="J33" s="2">
+        <v>1</v>
+      </c>
+      <c r="K33" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="2">
         <v>31</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="E34">
         <v>3001</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H34" s="2">
+        <v>138</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I34" s="2">
         <v>100</v>
       </c>
-      <c r="I34" s="2">
+      <c r="J34" s="2">
         <v>300</v>
       </c>
-      <c r="J34" s="2">
+      <c r="K34" s="2">
         <v>500</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="2">
         <v>32</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="E35">
         <v>3001</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H35" s="2">
+        <v>134</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I35" s="2">
         <v>100</v>
       </c>
-      <c r="I35" s="2">
-        <v>1</v>
-      </c>
       <c r="J35" s="2">
         <v>1</v>
       </c>
+      <c r="K35" s="2">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="17.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="18.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4" s="14"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="F5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5" s="14"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6" s="14"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H10" s="14"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H12" s="14"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="141">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="8" type="noConversion"/>
@@ -647,6 +647,10 @@
   </si>
   <si>
     <t>DropObjectGroupID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArcaneScroll</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1199,7 +1203,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3177,7 +3181,7 @@
         <v>1001</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>134</v>
@@ -3186,7 +3190,7 @@
         <v>68</v>
       </c>
       <c r="I13" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J13" s="2">
         <v>1</v>
@@ -3570,7 +3574,7 @@
         <v>68</v>
       </c>
       <c r="I25" s="2">
-        <v>0.5</v>
+        <v>15</v>
       </c>
       <c r="J25" s="2">
         <v>1</v>
@@ -3602,7 +3606,7 @@
         <v>69</v>
       </c>
       <c r="I26" s="2">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="J26" s="2">
         <v>1</v>
@@ -3753,7 +3757,7 @@
         <v>3001</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>134</v>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="6"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="136">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="8" type="noConversion"/>
@@ -347,14 +347,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>ArcaneScroll</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>비전 주문서</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>마력정수</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -395,10 +387,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>카드 구매창이 뜨게 하는 스크롤</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>체력을 25% 회복시키는 오브</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -443,10 +431,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>스킬 구매 목록</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>GroupID</t>
   </si>
   <si>
@@ -629,9 +613,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Prefab_DropItem_ArcaneScroll</t>
-  </si>
-  <si>
     <t>Prefab_DropItem_HealOrb</t>
   </si>
   <si>
@@ -650,7 +631,7 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>ArcaneScroll</t>
+    <t>SpawnPoint_01</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1203,7 +1184,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1211,7 +1192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="1" bestFit="1" customWidth="1"/>
@@ -1236,7 +1217,7 @@
         <v>17</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1244,7 +1225,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1252,7 +1233,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1260,7 +1241,7 @@
         <v>19</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1268,7 +1249,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1276,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D8" s="17"/>
     </row>
@@ -1285,7 +1266,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1293,7 +1274,7 @@
         <v>56</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1301,14 +1282,6 @@
         <v>62</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="19" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1340,7 +1313,7 @@
         <v>24</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -1360,16 +1333,16 @@
         <v>21</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>33</v>
@@ -1384,7 +1357,7 @@
         <v>36</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -1399,10 +1372,10 @@
         <v>22</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>14</v>
@@ -1431,14 +1404,14 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -1463,14 +1436,14 @@
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G5" s="2">
         <v>3</v>
@@ -1495,14 +1468,14 @@
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -1761,25 +1734,25 @@
         <v>21</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>23</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I2" s="9" t="s">
         <v>50</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>59</v>
@@ -1797,7 +1770,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>14</v>
@@ -1839,7 +1812,7 @@
         <v>10001</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K4">
         <v>2001</v>
@@ -1864,7 +1837,7 @@
         <v>10001</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K5">
         <v>2001</v>
@@ -1889,7 +1862,7 @@
         <v>10001</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K6">
         <v>2001</v>
@@ -1905,7 +1878,7 @@
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
@@ -1989,7 +1962,7 @@
       </c>
       <c r="D10" s="11"/>
       <c r="E10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F10">
         <v>30</v>
@@ -2073,14 +2046,14 @@
       </c>
       <c r="D13" s="11"/>
       <c r="E13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F13"/>
       <c r="H13" s="2">
         <v>10001</v>
       </c>
       <c r="J13" s="23" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K13">
         <v>1001</v>
@@ -2103,7 +2076,7 @@
         <v>10001</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K14">
         <v>1001</v>
@@ -2126,7 +2099,7 @@
         <v>10001</v>
       </c>
       <c r="J15" s="23" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K15">
         <v>1001</v>
@@ -2142,7 +2115,7 @@
       </c>
       <c r="D16" s="11"/>
       <c r="E16" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -2255,7 +2228,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C1" s="10"/>
     </row>
@@ -2268,7 +2241,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>5</v>
@@ -2306,7 +2279,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -2402,7 +2375,7 @@
         <v>24</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -2416,22 +2389,22 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -2452,10 +2425,10 @@
         <v>14</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -2469,7 +2442,7 @@
         <v>10001</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>135</v>
       </c>
       <c r="F4">
         <v>30</v>
@@ -2488,7 +2461,7 @@
         <v>10002</v>
       </c>
       <c r="E5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F5" s="2">
         <v>15</v>
@@ -2507,7 +2480,7 @@
         <v>10001</v>
       </c>
       <c r="E6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F6">
         <v>40</v>
@@ -2526,7 +2499,7 @@
         <v>10002</v>
       </c>
       <c r="E7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F7" s="2">
         <v>20</v>
@@ -2544,7 +2517,7 @@
         <v>10003</v>
       </c>
       <c r="E8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F8" s="2">
         <v>10</v>
@@ -2562,7 +2535,7 @@
         <v>10001</v>
       </c>
       <c r="E9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2582,7 +2555,7 @@
         <v>10002</v>
       </c>
       <c r="E10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -2602,7 +2575,7 @@
         <v>10003</v>
       </c>
       <c r="E11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -2622,7 +2595,7 @@
         <v>20001</v>
       </c>
       <c r="E12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -2642,7 +2615,7 @@
         <v>10001</v>
       </c>
       <c r="E13" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -2662,7 +2635,7 @@
         <v>10002</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -2682,7 +2655,7 @@
         <v>10003</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -2702,7 +2675,7 @@
         <v>10001</v>
       </c>
       <c r="E16" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F16" s="2">
         <v>50</v>
@@ -2720,7 +2693,7 @@
         <v>10001</v>
       </c>
       <c r="E17" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F17" s="2">
         <v>50</v>
@@ -2738,7 +2711,7 @@
         <v>10001</v>
       </c>
       <c r="E18" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F18" s="2">
         <v>50</v>
@@ -2756,7 +2729,7 @@
         <v>30001</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
@@ -2782,7 +2755,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
@@ -2825,25 +2798,25 @@
         <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I2" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -2861,16 +2834,16 @@
         <v>14</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J3" s="9" t="s">
         <v>14</v>
@@ -2887,7 +2860,7 @@
         <v>60</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E4">
         <v>1001</v>
@@ -2896,10 +2869,10 @@
         <v>55</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I4" s="2">
         <v>5</v>
@@ -2919,7 +2892,7 @@
         <v>60</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E5">
         <v>1001</v>
@@ -2928,10 +2901,10 @@
         <v>55</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I5" s="2">
         <v>15</v>
@@ -2951,7 +2924,7 @@
         <v>60</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E6">
         <v>1001</v>
@@ -2960,10 +2933,10 @@
         <v>55</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I6" s="2">
         <v>100</v>
@@ -2983,7 +2956,7 @@
         <v>61</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E7">
         <v>1001</v>
@@ -2992,10 +2965,10 @@
         <v>56</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I7" s="2">
         <v>5</v>
@@ -3015,7 +2988,7 @@
         <v>61</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E8">
         <v>1001</v>
@@ -3024,10 +2997,10 @@
         <v>56</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I8" s="2">
         <v>15</v>
@@ -3047,7 +3020,7 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E9">
         <v>1001</v>
@@ -3056,10 +3029,10 @@
         <v>56</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I9" s="2">
         <v>100</v>
@@ -3076,10 +3049,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E10">
         <v>1001</v>
@@ -3088,10 +3061,10 @@
         <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I10" s="2">
         <v>100</v>
@@ -3108,10 +3081,10 @@
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E11">
         <v>1001</v>
@@ -3120,10 +3093,10 @@
         <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I11" s="2">
         <v>100</v>
@@ -3140,10 +3113,10 @@
         <v>9</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E12">
         <v>1001</v>
@@ -3152,10 +3125,10 @@
         <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I12" s="2">
         <v>100</v>
@@ -3171,26 +3144,26 @@
       <c r="B13" s="2">
         <v>10</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>87</v>
+      <c r="C13" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="E13">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I13" s="2">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="J13" s="2">
         <v>1</v>
@@ -3203,26 +3176,26 @@
       <c r="B14" s="2">
         <v>11</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>87</v>
+      <c r="C14" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="E14">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I14" s="2">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="J14" s="2">
         <v>1</v>
@@ -3235,23 +3208,23 @@
       <c r="B15" s="2">
         <v>12</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>87</v>
+      <c r="C15" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="E15">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I15" s="2">
         <v>100</v>
@@ -3260,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -3268,22 +3241,22 @@
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E16">
         <v>2001</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I16" s="2">
         <v>2.5</v>
@@ -3300,22 +3273,22 @@
         <v>14</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E17">
         <v>2001</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I17" s="2">
         <v>7.5</v>
@@ -3332,22 +3305,22 @@
         <v>15</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E18">
         <v>2001</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I18" s="2">
         <v>100</v>
@@ -3364,31 +3337,31 @@
         <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E19">
         <v>2001</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I19" s="2">
-        <v>2.5</v>
+        <v>100</v>
       </c>
       <c r="J19" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K19" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
@@ -3396,31 +3369,31 @@
         <v>17</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E20">
         <v>2001</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I20" s="2">
-        <v>7.5</v>
+        <v>100</v>
       </c>
       <c r="J20" s="2">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K20" s="2">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.3">
@@ -3428,31 +3401,31 @@
         <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E21">
         <v>2001</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I21" s="2">
         <v>100</v>
       </c>
       <c r="J21" s="2">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="K21" s="2">
-        <v>2</v>
+        <v>500</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
@@ -3460,19 +3433,19 @@
         <v>19</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E22">
-        <v>2001</v>
+        <v>3001</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>68</v>
@@ -3481,10 +3454,10 @@
         <v>100</v>
       </c>
       <c r="J22" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K22" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.3">
@@ -3492,31 +3465,31 @@
         <v>20</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E23">
-        <v>2001</v>
+        <v>3001</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I23" s="2">
         <v>100</v>
       </c>
       <c r="J23" s="2">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K23" s="2">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
@@ -3524,22 +3497,22 @@
         <v>21</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E24">
-        <v>2001</v>
+        <v>3001</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I24" s="2">
         <v>100</v>
@@ -3555,352 +3528,96 @@
       <c r="B25" s="2">
         <v>22</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>87</v>
+      <c r="C25" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="E25">
-        <v>2001</v>
+        <v>3001</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>68</v>
       </c>
       <c r="I25" s="2">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="J25" s="2">
         <v>1</v>
       </c>
       <c r="K25" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <v>23</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>87</v>
+      <c r="C26" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="E26">
-        <v>2001</v>
+        <v>3001</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I26" s="2">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="J26" s="2">
         <v>1</v>
       </c>
       <c r="K26" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <v>24</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>87</v>
+      <c r="C27" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="E27">
-        <v>2001</v>
+        <v>3001</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I27" s="2">
         <v>100</v>
       </c>
       <c r="J27" s="2">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="K27" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B28" s="2">
-        <v>25</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E28">
-        <v>3001</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I28" s="2">
-        <v>100</v>
-      </c>
-      <c r="J28" s="2">
-        <v>1</v>
-      </c>
-      <c r="K28" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B29" s="2">
-        <v>26</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E29">
-        <v>3001</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I29" s="2">
-        <v>100</v>
-      </c>
-      <c r="J29" s="2">
-        <v>1</v>
-      </c>
-      <c r="K29" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B30" s="2">
-        <v>27</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E30">
-        <v>3001</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I30" s="2">
-        <v>100</v>
-      </c>
-      <c r="J30" s="2">
-        <v>300</v>
-      </c>
-      <c r="K30" s="2">
         <v>500</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B31" s="2">
-        <v>28</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E31">
-        <v>3001</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I31" s="2">
-        <v>100</v>
-      </c>
-      <c r="J31" s="2">
-        <v>1</v>
-      </c>
-      <c r="K31" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B32" s="2">
-        <v>29</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E32">
-        <v>3001</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I32" s="2">
-        <v>100</v>
-      </c>
-      <c r="J32" s="2">
-        <v>1</v>
-      </c>
-      <c r="K32" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B33" s="2">
-        <v>30</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E33">
-        <v>3001</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I33" s="2">
-        <v>100</v>
-      </c>
-      <c r="J33" s="2">
-        <v>1</v>
-      </c>
-      <c r="K33" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B34" s="2">
-        <v>31</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E34">
-        <v>3001</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I34" s="2">
-        <v>100</v>
-      </c>
-      <c r="J34" s="2">
-        <v>300</v>
-      </c>
-      <c r="K34" s="2">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B35" s="2">
-        <v>32</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E35">
-        <v>3001</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I35" s="2">
-        <v>100</v>
-      </c>
-      <c r="J35" s="2">
-        <v>1</v>
-      </c>
-      <c r="K35" s="2">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3940,7 +3657,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -3956,7 +3673,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
@@ -3972,7 +3689,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4"/>
@@ -3986,7 +3703,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D5" s="11"/>
       <c r="F5"/>
@@ -3999,7 +3716,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6"/>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,17 +4,17 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
     <sheet name="#Dungeon" sheetId="18" r:id="rId2"/>
     <sheet name="#StageGroup" sheetId="16" r:id="rId3"/>
     <sheet name="#Stage" sheetId="17" r:id="rId4"/>
-    <sheet name="#MapData" sheetId="15" r:id="rId5"/>
-    <sheet name="#MonsterSpawn" sheetId="21" r:id="rId6"/>
-    <sheet name="#DropObject" sheetId="19" r:id="rId7"/>
-    <sheet name="#StageReward" sheetId="20" r:id="rId8"/>
+    <sheet name="#DungeonReward" sheetId="20" r:id="rId5"/>
+    <sheet name="#MapData" sheetId="15" r:id="rId6"/>
+    <sheet name="#MonsterSpawn" sheetId="21" r:id="rId7"/>
+    <sheet name="#DropObject" sheetId="19" r:id="rId8"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -66,38 +66,38 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="142">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>BGM</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>빙하</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>용암</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Sound_Map_2</t>
@@ -110,55 +110,51 @@
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>지옥</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MapModeType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>BuildingDestroy</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Defense</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Capture</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Breakthrough</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>BossBattle</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>LimitTime</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -175,15 +171,15 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>초원</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageGroup</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -199,15 +195,15 @@
       </rPr>
       <t>int</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageID_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageID_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageID_3</t>
@@ -220,11 +216,11 @@
   </si>
   <si>
     <t>StageGroupID_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageGroupID_3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageGroupID_4</t>
@@ -234,19 +230,19 @@
   </si>
   <si>
     <t>건물 파괴 1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>디펜스 1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>디펜스 1-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>디펜스 1-3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>건물 파괴 1-2</t>
@@ -256,47 +252,47 @@
   </si>
   <si>
     <t>점령 1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>점령 1-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>점령 1-3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>돌파 1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>돌파 1-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>돌파 1-3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>보스전 1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MapObjectIDs</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>던전1의  스테이지1 그룹</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>던전1의  스테이지2 그룹</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>던전1의  스테이지3 그룹</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -312,305 +308,297 @@
       </rPr>
       <t xml:space="preserve"> 추가 스테이지 그룹</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>HealOrb</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StaminaOrb</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StageReward</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DropObject</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StageRewardIDs</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>체력 회복 구슬</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>스태미너 회복 구슬</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MagicEssence</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>마력정수</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!MonsterTypes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Elite</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Boss</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DropChance</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MinCount</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MaxCount</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>체력을 25% 회복시키는 오브</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>스태미너를 25% 회복 시키는 오브</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>카드구매용 임시재화</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>적 웨이브가 n번 오고 모두 섬멸</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>지정된 공간에서 n초 동안 버티면 승리</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>적 저자선을 뚫고 지정된 위치로 이동하면 승리</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>보스를 n마리 죽이면 승리</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>지정된 건물을 n개 파괴하면 승리</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>체력 25% 회복</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>스태미너 25% 회복</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>스킬 구매 재화</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>GroupID</t>
   </si>
   <si>
     <t>GroupID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>10001;10002</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SpawnPoint_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SpawnPoint_02</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SpawnPoint_03</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>40001;40002;40003</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DropObjectType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!DropObjectType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RecommandedLvText</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>1 ~ 5</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>5 ~ 10</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>10 ~ 15</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Dungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Icon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Image_Stage_1</t>
   </si>
   <si>
     <t>Image_Stage_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>1. 고블린 숲(쉬움)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>2. 고블린 숲(보통)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>3. 고블린 숲(어려움)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ExtraStageGroupID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ModeType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>BuildingDestroy</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Capture</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Breakthrough</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>BossBattle</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ClearValue</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!MapModeType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MapID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterSpawnGroupIDs</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MapData</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Sound_Map_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MapPrefab</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterSpawn</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SpawnPoint</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SpawnStepCount</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SpawnAllCount</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SpawnStepDelay</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>TotalStageCount</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageGroupID_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DropObjectType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_DropItem_HealOrb</t>
@@ -620,19 +608,79 @@
   </si>
   <si>
     <t>Path</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_DropItem_MagicEssence</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DropObjectGroupID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SpawnPoint_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageRound</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonID</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ungeon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Reward</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>10002;50001;60001</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageFixRewardIDs</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageRollRewardIDs</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001;20001;30001;40001</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -642,12 +690,20 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -831,12 +887,12 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -850,46 +906,46 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -901,14 +957,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1208,48 +1270,48 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1" s="17"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1257,36 +1319,36 @@
         <v>0</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D8" s="17"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1310,10 +1372,10 @@
   <sheetData>
     <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -1330,73 +1392,73 @@
         <v>11</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="M2" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -1404,14 +1466,14 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G4">
         <v>3</v>
@@ -1436,14 +1498,14 @@
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G5" s="2">
         <v>3</v>
@@ -1468,14 +1530,14 @@
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -1505,7 +1567,7 @@
       <c r="J12" s="14"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1532,7 +1594,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -1551,19 +1613,19 @@
         <v>11</v>
       </c>
       <c r="D2" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="H2" s="15" t="s">
         <v>31</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>32</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
@@ -1577,19 +1639,19 @@
         <v>1</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
@@ -1599,7 +1661,7 @@
         <v>10001</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2">
         <v>10001</v>
@@ -1620,7 +1682,7 @@
         <v>10002</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" s="2">
         <v>10002</v>
@@ -1641,7 +1703,7 @@
         <v>10003</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="2">
         <v>10003</v>
@@ -1662,7 +1724,7 @@
         <v>10004</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" s="14">
         <v>50001</v>
@@ -1689,14 +1751,14 @@
       <c r="E18" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
@@ -1706,23 +1768,22 @@
     <col min="9" max="9" width="19.125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.5" style="23" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>134</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
       <c r="J1" s="20"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="9" t="s">
         <v>2</v>
@@ -1731,79 +1792,73 @@
         <v>11</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F2" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J2" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>116</v>
-      </c>
       <c r="K2" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>10001</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -1812,23 +1867,22 @@
         <v>10001</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K4">
         <v>2001</v>
       </c>
-      <c r="L4"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>10002</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -1837,23 +1891,22 @@
         <v>10001</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K5">
         <v>2001</v>
       </c>
-      <c r="L5"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>10003</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -1862,23 +1915,22 @@
         <v>10001</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K6">
         <v>2001</v>
       </c>
-      <c r="L6"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>20001</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
@@ -1895,18 +1947,17 @@
       <c r="K7">
         <v>1001</v>
       </c>
-      <c r="L7"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>20002</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
@@ -1923,18 +1974,17 @@
       <c r="K8">
         <v>1001</v>
       </c>
-      <c r="L8"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>20003</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" s="2">
         <v>1</v>
@@ -1951,18 +2001,17 @@
       <c r="K9">
         <v>1001</v>
       </c>
-      <c r="L9"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>30001</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F10">
         <v>30</v>
@@ -1979,18 +2028,17 @@
       <c r="K10">
         <v>2001</v>
       </c>
-      <c r="L10"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>30002</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11">
         <v>30</v>
@@ -2007,18 +2055,17 @@
       <c r="K11">
         <v>2001</v>
       </c>
-      <c r="L11"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>30003</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12">
         <v>30</v>
@@ -2035,87 +2082,83 @@
       <c r="K12">
         <v>2001</v>
       </c>
-      <c r="L12"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>40001</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F13"/>
       <c r="H13" s="2">
         <v>10001</v>
       </c>
       <c r="J13" s="23" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K13">
         <v>1001</v>
       </c>
-      <c r="L13"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>40002</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" s="11"/>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F14"/>
       <c r="H14" s="2">
         <v>10001</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K14">
         <v>1001</v>
       </c>
-      <c r="L14"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>40003</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" s="11"/>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15"/>
       <c r="H15" s="2">
         <v>10001</v>
       </c>
       <c r="J15" s="23" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K15">
         <v>1001</v>
       </c>
-      <c r="L15"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>50001</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -2129,46 +2172,40 @@
       <c r="K16">
         <v>3001</v>
       </c>
-      <c r="L16"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17"/>
       <c r="F17"/>
       <c r="K17"/>
-      <c r="L17"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18"/>
       <c r="F18"/>
       <c r="K18"/>
-      <c r="L18"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="3:11" x14ac:dyDescent="0.3">
       <c r="I20"/>
       <c r="J20" s="25"/>
       <c r="K20"/>
-      <c r="L20"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.3">
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
       <c r="F21"/>
       <c r="I21"/>
       <c r="J21" s="25"/>
       <c r="K21"/>
-      <c r="L21"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.3">
       <c r="I22"/>
       <c r="J22" s="25"/>
       <c r="K22"/>
-      <c r="L22"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
@@ -2176,38 +2213,391 @@
       <c r="I23"/>
       <c r="J23" s="25"/>
       <c r="K23"/>
-      <c r="L23"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="3:11" x14ac:dyDescent="0.3">
       <c r="I24" s="5"/>
       <c r="J24" s="25"/>
       <c r="K24"/>
-      <c r="L24"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25"/>
       <c r="J25" s="25"/>
     </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:11" x14ac:dyDescent="0.3">
       <c r="J26" s="25"/>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:11" x14ac:dyDescent="0.3">
       <c r="J27" s="25"/>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:11" x14ac:dyDescent="0.3">
       <c r="J28" s="25"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R20"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.75" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.125" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="18.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="18.5" style="2" customWidth="1"/>
+    <col min="18" max="18" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F4" s="23">
+        <v>50001</v>
+      </c>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4" s="14"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F5" s="23">
+        <v>50001</v>
+      </c>
+      <c r="K5" s="11"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5" s="14"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="23">
+        <v>50001</v>
+      </c>
+      <c r="K6" s="11"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6" s="14"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <v>4</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="L7"/>
+      <c r="M7"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F8" s="23">
+        <v>50001</v>
+      </c>
+      <c r="L8"/>
+      <c r="M8"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F9" s="23">
+        <v>50001</v>
+      </c>
+      <c r="L9"/>
+      <c r="M9"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F10" s="23">
+        <v>50001</v>
+      </c>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="O10" s="14"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="O11" s="14"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F12" s="23">
+        <v>50001</v>
+      </c>
+      <c r="O12" s="14"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" s="23">
+        <v>50001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
+        <v>3</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F14" s="23">
+        <v>50001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2">
+        <v>4</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+    </row>
+    <row r="19" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+    </row>
+    <row r="20" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2228,7 +2618,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C1" s="10"/>
     </row>
@@ -2241,7 +2631,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>5</v>
@@ -2273,13 +2663,13 @@
         <v>10001</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -2349,13 +2739,13 @@
       <c r="C20" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2372,10 +2762,10 @@
   <sheetData>
     <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -2389,46 +2779,46 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>87</v>
-      </c>
       <c r="E2" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="G2" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -2442,7 +2832,7 @@
         <v>10001</v>
       </c>
       <c r="E4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F4">
         <v>30</v>
@@ -2461,7 +2851,7 @@
         <v>10002</v>
       </c>
       <c r="E5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F5" s="2">
         <v>15</v>
@@ -2480,7 +2870,7 @@
         <v>10001</v>
       </c>
       <c r="E6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F6">
         <v>40</v>
@@ -2499,7 +2889,7 @@
         <v>10002</v>
       </c>
       <c r="E7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F7" s="2">
         <v>20</v>
@@ -2517,7 +2907,7 @@
         <v>10003</v>
       </c>
       <c r="E8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F8" s="2">
         <v>10</v>
@@ -2535,7 +2925,7 @@
         <v>10001</v>
       </c>
       <c r="E9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2555,7 +2945,7 @@
         <v>10002</v>
       </c>
       <c r="E10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -2575,7 +2965,7 @@
         <v>10003</v>
       </c>
       <c r="E11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -2595,7 +2985,7 @@
         <v>20001</v>
       </c>
       <c r="E12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -2615,7 +3005,7 @@
         <v>10001</v>
       </c>
       <c r="E13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -2635,7 +3025,7 @@
         <v>10002</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -2655,7 +3045,7 @@
         <v>10003</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -2675,7 +3065,7 @@
         <v>10001</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F16" s="2">
         <v>50</v>
@@ -2693,7 +3083,7 @@
         <v>10001</v>
       </c>
       <c r="E17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F17" s="2">
         <v>50</v>
@@ -2711,7 +3101,7 @@
         <v>10001</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F18" s="2">
         <v>50</v>
@@ -2729,7 +3119,7 @@
         <v>30001</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
@@ -2748,12 +3138,12 @@
       <c r="B23"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2772,10 +3162,10 @@
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -2795,61 +3185,61 @@
         <v>11</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -2857,22 +3247,22 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E4">
         <v>1001</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I4" s="2">
         <v>5</v>
@@ -2889,22 +3279,22 @@
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E5">
         <v>1001</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I5" s="2">
         <v>15</v>
@@ -2921,22 +3311,22 @@
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E6">
         <v>1001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I6" s="2">
         <v>100</v>
@@ -2953,22 +3343,22 @@
         <v>4</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E7">
         <v>1001</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I7" s="2">
         <v>5</v>
@@ -2985,22 +3375,22 @@
         <v>5</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E8">
         <v>1001</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I8" s="2">
         <v>15</v>
@@ -3017,22 +3407,22 @@
         <v>6</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E9">
         <v>1001</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I9" s="2">
         <v>100</v>
@@ -3049,22 +3439,22 @@
         <v>7</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E10">
         <v>1001</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I10" s="2">
         <v>100</v>
@@ -3081,22 +3471,22 @@
         <v>8</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E11">
         <v>1001</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I11" s="2">
         <v>100</v>
@@ -3113,22 +3503,22 @@
         <v>9</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E12">
         <v>1001</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I12" s="2">
         <v>100</v>
@@ -3145,22 +3535,22 @@
         <v>10</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E13">
         <v>2001</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I13" s="2">
         <v>2.5</v>
@@ -3177,22 +3567,22 @@
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E14">
         <v>2001</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I14" s="2">
         <v>7.5</v>
@@ -3209,22 +3599,22 @@
         <v>12</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E15">
         <v>2001</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I15" s="2">
         <v>100</v>
@@ -3241,22 +3631,22 @@
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E16">
         <v>2001</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I16" s="2">
         <v>2.5</v>
@@ -3273,22 +3663,22 @@
         <v>14</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E17">
         <v>2001</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I17" s="2">
         <v>7.5</v>
@@ -3305,22 +3695,22 @@
         <v>15</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E18">
         <v>2001</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I18" s="2">
         <v>100</v>
@@ -3337,22 +3727,22 @@
         <v>16</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E19">
         <v>2001</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I19" s="2">
         <v>100</v>
@@ -3369,22 +3759,22 @@
         <v>17</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E20">
         <v>2001</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I20" s="2">
         <v>100</v>
@@ -3401,22 +3791,22 @@
         <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E21">
         <v>2001</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I21" s="2">
         <v>100</v>
@@ -3433,22 +3823,22 @@
         <v>19</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E22">
         <v>3001</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I22" s="2">
         <v>100</v>
@@ -3465,22 +3855,22 @@
         <v>20</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E23">
         <v>3001</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I23" s="2">
         <v>100</v>
@@ -3497,22 +3887,22 @@
         <v>21</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E24">
         <v>3001</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I24" s="2">
         <v>100</v>
@@ -3529,22 +3919,22 @@
         <v>22</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E25">
         <v>3001</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I25" s="2">
         <v>100</v>
@@ -3561,22 +3951,22 @@
         <v>23</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E26">
         <v>3001</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I26" s="2">
         <v>100</v>
@@ -3593,22 +3983,22 @@
         <v>24</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E27">
         <v>3001</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I27" s="2">
         <v>100</v>
@@ -3621,121 +4011,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="17.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="18.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="11"/>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4" s="14"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="2">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="11"/>
-      <c r="F5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5" s="14"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="2">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6" s="14"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H10" s="14"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H11" s="14"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H12" s="14"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="146">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="9" type="noConversion"/>
@@ -631,11 +631,23 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>StageRound</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DungeonID</t>
+    <t>10002;50001;60001</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001;20001;30001;40001</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClearExp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExtraClearExp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -667,19 +679,23 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>10002;50001;60001</t>
+    <t>DungeonID</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageRollRewardIDs</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StageRound</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001;20001;30001;40001</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>StageFixRewardIDs</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StageRollRewardIDs</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001;20001;30001;40001</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -892,7 +908,7 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -971,6 +987,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1246,7 +1265,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1355,7 +1374,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
@@ -1367,10 +1386,12 @@
     <col min="8" max="8" width="18.5" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="12" width="18.5" style="2" customWidth="1"/>
     <col min="13" max="13" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="14" max="14" width="8.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>23</v>
       </c>
@@ -1383,7 +1404,7 @@
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="9" t="s">
         <v>2</v>
@@ -1421,8 +1442,14 @@
       <c r="M2" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="2" t="s">
         <v>13</v>
@@ -1460,8 +1487,14 @@
       <c r="M3" s="9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N3" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>1</v>
       </c>
@@ -1492,8 +1525,14 @@
       <c r="M4" s="14">
         <v>10004</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N4" s="2">
+        <v>500</v>
+      </c>
+      <c r="O4" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>2</v>
       </c>
@@ -1524,8 +1563,14 @@
       <c r="M5" s="14">
         <v>10004</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="O5" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>3</v>
       </c>
@@ -1556,14 +1601,20 @@
       <c r="M6" s="14">
         <v>10004</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N6" s="2">
+        <v>1500</v>
+      </c>
+      <c r="O6" s="2">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J10" s="14"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J11" s="14"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J12" s="14"/>
     </row>
   </sheetData>
@@ -2269,8 +2320,8 @@
       <c r="A1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>137</v>
+      <c r="B1" s="29" t="s">
+        <v>140</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -2289,16 +2340,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="H2" s="9"/>
       <c r="J2" s="9"/>
@@ -2347,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F4" s="23">
         <v>50001</v>
@@ -2369,7 +2420,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F5" s="23">
         <v>50001</v>
@@ -2392,7 +2443,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F6" s="23">
         <v>50001</v>
@@ -2415,7 +2466,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="L7"/>
       <c r="M7"/>
@@ -2431,7 +2482,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F8" s="23">
         <v>50001</v>
@@ -2450,7 +2501,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F9" s="23">
         <v>50001</v>
@@ -2469,7 +2520,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F10" s="23">
         <v>50001</v>
@@ -2489,7 +2540,7 @@
         <v>4</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O11" s="14"/>
     </row>
@@ -2504,7 +2555,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F12" s="23">
         <v>50001</v>
@@ -2522,7 +2573,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F13" s="23">
         <v>50001</v>
@@ -2539,7 +2590,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F14" s="23">
         <v>50001</v>
@@ -2556,7 +2607,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="5:10" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -146,10 +146,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Map_Town</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>M</t>
     </r>
@@ -471,6 +467,10 @@
   </si>
   <si>
     <t>MapPrefab</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Map_Town</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1004,23 +1004,23 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1055,7 +1055,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1078,10 +1078,10 @@
         <v>12</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>4</v>
@@ -1107,7 +1107,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>11</v>
@@ -1128,20 +1128,20 @@
         <v>10001</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -1159,16 +1159,16 @@
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I5"/>
       <c r="L5"/>
@@ -1184,16 +1184,16 @@
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I6"/>
       <c r="L6"/>
@@ -1208,16 +1208,16 @@
         <v>19</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1228,16 +1228,16 @@
         <v>20</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1248,16 +1248,16 @@
         <v>21</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1268,16 +1268,16 @@
         <v>23</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K10" s="11"/>
     </row>
@@ -1286,19 +1286,19 @@
         <v>30101</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K11" s="11"/>
     </row>
@@ -1307,19 +1307,19 @@
         <v>30102</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K12" s="11"/>
     </row>
@@ -1328,19 +1328,19 @@
         <v>30201</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K13" s="11"/>
     </row>
@@ -1349,19 +1349,19 @@
         <v>30202</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1396,7 +1396,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1419,7 +1419,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
@@ -1457,11 +1457,11 @@
         <v>1</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1478,11 +1478,11 @@
         <v>2</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -1537,7 +1537,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -1546,16 +1546,16 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
         <v>36</v>
       </c>
-      <c r="D2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>37</v>
-      </c>
-      <c r="F2" t="s">
-        <v>38</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
@@ -1714,10 +1714,10 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1731,64 +1731,64 @@
         <v>2</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" t="s">
         <v>86</v>
       </c>
-      <c r="G2" t="s">
-        <v>87</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -1796,10 +1796,10 @@
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F4" s="2">
         <v>5</v>
@@ -1808,7 +1808,7 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I4" s="2">
         <v>500</v>
@@ -1822,10 +1822,10 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -1834,7 +1834,7 @@
         <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I5" s="2">
         <v>500</v>
@@ -1883,7 +1883,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1901,19 +1901,19 @@
         <v>15</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>16</v>
@@ -1925,22 +1925,22 @@
         <v>6</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>10</v>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
     <sheet name="#Map" sheetId="22" r:id="rId2"/>
     <sheet name="#Act" sheetId="23" r:id="rId3"/>
-    <sheet name="#MapStage" sheetId="24" r:id="rId4"/>
+    <sheet name="#Field" sheetId="24" r:id="rId4"/>
     <sheet name="#Dungeon" sheetId="25" r:id="rId5"/>
     <sheet name="#DungeonStage" sheetId="18" r:id="rId6"/>
   </sheets>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="106">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="8" type="noConversion"/>
@@ -171,112 +171,46 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
+    <t>Dungeon</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마을</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!MapType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Act</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Order</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReqLevel</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReqQuestID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>Stage</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Dungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마을</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!MapType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Act</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Order</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapStage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReqLevel</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReqQuestID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Image_GoldDungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Image_Town</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Image_Stage_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Image_Stage_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Image_ExpDungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map_Stage_1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map_Stage_1-2</t>
-  </si>
-  <si>
-    <t>Map_Stage_1-3</t>
-  </si>
-  <si>
-    <t>Map_Stage_2-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map_Stage_2-2</t>
-  </si>
-  <si>
-    <t>Map_Stage_2-3</t>
-  </si>
-  <si>
-    <t>Map_GoldDungeon_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map_GoldDungeon_2</t>
-  </si>
-  <si>
-    <t>Map_ExpDungeon_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Map_ExpDungeon_2</t>
-  </si>
-  <si>
     <t>Sound_GoldDungeon</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -286,14 +220,6 @@
   </si>
   <si>
     <t>Sound_Town</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sound_Stage_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sound_Stage_2</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -470,7 +396,98 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Map_Town</t>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Field</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_Field_1-1</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_1-2</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_1-3</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-2</t>
+  </si>
+  <si>
+    <t>Sound_Act1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound_Act2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_Town</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_GoldDungeon</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_GoldDungeon</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_ExpDungeon</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Town</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_1-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_1-2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_1-3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_2-1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_2-2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_2-3</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_GoldDungeon</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_ExpDungeon</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -660,7 +677,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -704,6 +721,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -980,7 +1000,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1015,12 +1035,12 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1040,7 +1060,7 @@
     <col min="4" max="4" width="11.75" style="2" customWidth="1"/>
     <col min="5" max="5" width="22.625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.25" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.5" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="18.5" style="2" customWidth="1"/>
@@ -1078,10 +1098,10 @@
         <v>12</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>4</v>
@@ -1107,7 +1127,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>11</v>
@@ -1128,20 +1148,20 @@
         <v>10001</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="10" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -1159,16 +1179,16 @@
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="I5"/>
       <c r="L5"/>
@@ -1184,16 +1204,16 @@
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="I6"/>
       <c r="L6"/>
@@ -1208,16 +1228,16 @@
         <v>19</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1228,16 +1248,16 @@
         <v>20</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1248,16 +1268,16 @@
         <v>21</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1268,16 +1288,16 @@
         <v>23</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="K10" s="11"/>
     </row>
@@ -1286,19 +1306,19 @@
         <v>30101</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="K11" s="11"/>
     </row>
@@ -1307,19 +1327,19 @@
         <v>30102</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="K12" s="11"/>
     </row>
@@ -1328,19 +1348,19 @@
         <v>30201</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="K13" s="11"/>
     </row>
@@ -1349,19 +1369,19 @@
         <v>30202</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1396,7 +1416,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1419,7 +1439,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
@@ -1457,11 +1477,11 @@
         <v>1</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1478,11 +1498,11 @@
         <v>2</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -1536,26 +1556,26 @@
       <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>34</v>
+      <c r="B1" s="17" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="8" t="s">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
         <v>33</v>
       </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
@@ -1714,10 +1734,10 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1731,64 +1751,64 @@
         <v>2</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -1796,10 +1816,10 @@
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F4" s="2">
         <v>5</v>
@@ -1808,7 +1828,7 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="I4" s="2">
         <v>500</v>
@@ -1822,10 +1842,10 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -1834,7 +1854,7 @@
         <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="I5" s="2">
         <v>500</v>
@@ -1883,7 +1903,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1901,19 +1921,19 @@
         <v>15</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>16</v>
@@ -1925,22 +1945,22 @@
         <v>6</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>10</v>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -38,35 +38,35 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="106">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>BGM</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -83,67 +83,67 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Icon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Icon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Gold</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Exp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DungeonType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RewardGroupID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>고블린 숲</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>고블린 제단</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>코볼트 광산</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>코볼트 부락</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>고블린 부락</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>코볼트 늪지대</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -160,165 +160,165 @@
       </rPr>
       <t>ap</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MapType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Town</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Dungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>마을</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!MapType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Act</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Order</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ActID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ReqLevel</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ReqQuestID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Stage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Sound_GoldDungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Sound_ExpDungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Sound_Town</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>액트1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>액트2</t>
   </si>
   <si>
     <t>Image_Act_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Image_Act_2</t>
   </si>
   <si>
     <t>RewardExp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>경험치 던전 - 숲</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>경험치 던전 - 동굴</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>골드던전 - 광산</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>골드던전 - 마을</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterLevel</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MapID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DungeonStage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MonsterSpawnGroupIDs</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Dungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>골드 던전</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>경험치 던전</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>대량의 경험치 획득 가능</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>대량의 골드 획득 가능</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DefaultEnterCount</t>
@@ -328,7 +328,7 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -345,150 +345,151 @@
       </rPr>
       <t>EnumTable</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!Dungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Icon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!Currency</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RevivalCostType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RevivalCost</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RevivalCostStep</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Dia</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Ruby</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MaxRevivalCount</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MapPrefab</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Field</t>
   </si>
   <si>
     <t>Field</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MapType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MapPrefab_Field_1-1</t>
   </si>
   <si>
+    <t>MapPrefab_Field_1-3</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-2</t>
+  </si>
+  <si>
+    <t>Sound_Act1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound_Act2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_Town</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_GoldDungeon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_GoldDungeon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_ExpDungeon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Town</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_1-1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_1-2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_1-3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_2-1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_2-2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_2-3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_GoldDungeon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_ExpDungeon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>MapPrefab_Field_1-2</t>
-  </si>
-  <si>
-    <t>MapPrefab_Field_1-3</t>
-  </si>
-  <si>
-    <t>MapPrefab_Field_2-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_Field_2-2</t>
-  </si>
-  <si>
-    <t>Sound_Act1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sound_Act2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_Town</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_Field_2-3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_GoldDungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_GoldDungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_ExpDungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Town</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_1-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_1-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_1-3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_2-1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_2-2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_2-3</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_GoldDungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_ExpDungeon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -498,12 +499,20 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -672,10 +681,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -691,39 +700,39 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1000,7 +1009,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1044,7 +1053,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1152,13 +1161,13 @@
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>39</v>
@@ -1179,7 +1188,7 @@
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>81</v>
@@ -1188,7 +1197,7 @@
         <v>85</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I5"/>
       <c r="L5"/>
@@ -1204,16 +1213,16 @@
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I6"/>
       <c r="L6"/>
@@ -1228,16 +1237,16 @@
         <v>19</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1248,16 +1257,16 @@
         <v>20</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1268,16 +1277,16 @@
         <v>21</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1288,16 +1297,16 @@
         <v>23</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K10" s="11"/>
     </row>
@@ -1309,13 +1318,13 @@
         <v>48</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>37</v>
@@ -1330,13 +1339,13 @@
         <v>49</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>37</v>
@@ -1351,13 +1360,13 @@
         <v>46</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>38</v>
@@ -1372,20 +1381,20 @@
         <v>47</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -1529,7 +1538,7 @@
       <c r="J12" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1708,7 +1717,7 @@
       <c r="G12" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1876,7 +1885,7 @@
       <c r="H10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -2023,7 +2032,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -1009,7 +1009,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="109">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="9" type="noConversion"/>
@@ -110,14 +110,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>DungeonType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>RewardGroupID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>!int</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -207,10 +199,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Stage</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>Sound_GoldDungeon</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -237,10 +225,6 @@
     <t>Image_Act_2</t>
   </si>
   <si>
-    <t>RewardExp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>!int</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -265,31 +249,11 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>MonsterLevel</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>!int</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>MapID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DungeonStage</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterSpawnGroupIDs</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dungeon</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -380,10 +344,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>Dia</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>Ruby</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -440,18 +400,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>MapPrefab_GoldDungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_GoldDungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_ExpDungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>Icon_Town</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -489,6 +437,70 @@
   </si>
   <si>
     <t>MapPrefab_Field_1-2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_GoldDungeon_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_GoldDungeon_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_ExpDungeon_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_ExpDungeon_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpawnGroupIDs</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dungeon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>2001;2002;2003</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonStage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonType</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapID</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterLevel</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardExp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardGroupID</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>TimeLimit</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -726,13 +738,13 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1009,7 +1021,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1033,23 +1045,23 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1084,7 +1096,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1107,10 +1119,10 @@
         <v>12</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>4</v>
@@ -1136,7 +1148,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>11</v>
@@ -1157,20 +1169,20 @@
         <v>10001</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="10" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -1184,20 +1196,20 @@
         <v>20101</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I5"/>
       <c r="L5"/>
@@ -1209,20 +1221,20 @@
         <v>20102</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I6"/>
       <c r="L6"/>
@@ -1234,19 +1246,19 @@
         <v>20103</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1254,19 +1266,19 @@
         <v>20201</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1274,19 +1286,19 @@
         <v>20202</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1294,19 +1306,19 @@
         <v>20203</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K10" s="11"/>
     </row>
@@ -1315,19 +1327,19 @@
         <v>30101</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>93</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K11" s="11"/>
     </row>
@@ -1336,19 +1348,19 @@
         <v>30102</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>94</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K12" s="11"/>
     </row>
@@ -1357,19 +1369,19 @@
         <v>30201</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K13" s="11"/>
     </row>
@@ -1378,19 +1390,19 @@
         <v>30202</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1425,7 +1437,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1448,7 +1460,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
@@ -1471,7 +1483,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
@@ -1486,11 +1498,11 @@
         <v>1</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1507,11 +1519,11 @@
         <v>2</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -1565,26 +1577,26 @@
       <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>82</v>
+      <c r="B1" s="16" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="8" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
         <v>32</v>
-      </c>
-      <c r="D2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" t="s">
-        <v>34</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
@@ -1596,16 +1608,16 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
@@ -1742,11 +1754,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>57</v>
+      <c r="A1" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>98</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1760,64 +1772,64 @@
         <v>2</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="G2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -1825,10 +1837,10 @@
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F4" s="2">
         <v>5</v>
@@ -1837,7 +1849,7 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I4" s="2">
         <v>500</v>
@@ -1851,10 +1863,10 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -1863,7 +1875,7 @@
         <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="I5" s="2">
         <v>500</v>
@@ -1893,7 +1905,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="7" bestFit="1" customWidth="1"/>
@@ -1901,18 +1913,18 @@
     <col min="3" max="3" width="14.375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="14.375" style="2" customWidth="1"/>
     <col min="6" max="6" width="23.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="10.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="7" max="8" width="14.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>55</v>
+      <c r="B1" s="17" t="s">
+        <v>100</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1920,62 +1932,69 @@
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
       <c r="H1" s="9"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I1" s="9"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>10001</v>
       </c>
@@ -1988,8 +2007,17 @@
       <c r="E4" s="2">
         <v>30101</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>10002</v>
       </c>
@@ -2002,8 +2030,14 @@
       <c r="E5" s="2">
         <v>30102</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G5" s="2">
+        <v>50</v>
+      </c>
+      <c r="H5" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>20001</v>
       </c>
@@ -2016,8 +2050,14 @@
       <c r="E6" s="2">
         <v>30201</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>20002</v>
       </c>
@@ -2029,6 +2069,12 @@
       </c>
       <c r="E7" s="2">
         <v>30202</v>
+      </c>
+      <c r="G7" s="2">
+        <v>50</v>
+      </c>
+      <c r="H7" s="2">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -35,38 +35,38 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="110">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BGM</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -83,59 +83,59 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Icon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Icon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Gold</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Exp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>고블린 숲</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>고블린 제단</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>코볼트 광산</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>코볼트 부락</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>고블린 부락</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>코볼트 늪지대</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -152,137 +152,137 @@
       </rPr>
       <t>ap</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>MapType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Town</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Dungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>마을</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!MapType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Act</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Order</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>ActID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>ReqLevel</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>ReqQuestID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Sound_GoldDungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Sound_ExpDungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Sound_Town</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>액트1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>액트2</t>
   </si>
   <si>
     <t>Image_Act_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Image_Act_2</t>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>경험치 던전 - 숲</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>경험치 던전 - 동굴</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>골드던전 - 광산</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>골드던전 - 마을</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>골드 던전</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>경험치 던전</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>대량의 경험치 획득 가능</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>대량의 골드 획득 가능</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>DefaultEnterCount</t>
@@ -292,7 +292,7 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -309,199 +309,203 @@
       </rPr>
       <t>EnumTable</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!Dungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Icon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!Currency</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ruby</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Field</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapType</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ID</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_Field_1-1</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_1-3</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-2</t>
+  </si>
+  <si>
+    <t>Sound_Act1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sound_Act2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_Town</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-3</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Town</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_1-1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_1-2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_1-3</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_2-1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_2-2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_2-3</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_GoldDungeon</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_ExpDungeon</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_Field_1-2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_GoldDungeon_1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_GoldDungeon_2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_ExpDungeon_1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_ExpDungeon_2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpawnGroupIDs</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dungeon</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>2001;2002;2003</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonStage</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonType</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapID</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterLevel</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardExp</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardGroupID</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>TimeLimit</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxRevivalCount</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>RevivalCostType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>RevivalCost</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>RevivalCostStep</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ruby</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxRevivalCount</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Field</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!ID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_Field_1-1</t>
-  </si>
-  <si>
-    <t>MapPrefab_Field_1-3</t>
-  </si>
-  <si>
-    <t>MapPrefab_Field_2-1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_Field_2-2</t>
-  </si>
-  <si>
-    <t>Sound_Act1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sound_Act2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_Town</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_Field_2-3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Town</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_1-1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_1-2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_1-3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_2-1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_2-2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_2-3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_GoldDungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_ExpDungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_Field_1-2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_GoldDungeon_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_GoldDungeon_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_ExpDungeon_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_ExpDungeon_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterSpawnGroupIDs</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>2001;2002;2003</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DungeonStage</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DungeonType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stage</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterLevel</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>RewardExp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>RewardGroupID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>TimeLimit</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>RevivalCostRatioStep</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -511,12 +515,20 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -693,10 +705,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -712,39 +724,39 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1021,7 +1033,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1056,7 +1068,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1065,7 +1077,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1119,10 +1131,10 @@
         <v>12</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>4</v>
@@ -1173,13 +1185,13 @@
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>36</v>
@@ -1200,16 +1212,16 @@
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="H5" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="I5"/>
       <c r="L5"/>
@@ -1225,16 +1237,16 @@
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I6"/>
       <c r="L6"/>
@@ -1249,16 +1261,16 @@
         <v>17</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1269,16 +1281,16 @@
         <v>18</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1289,16 +1301,16 @@
         <v>19</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1309,16 +1321,16 @@
         <v>21</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K10" s="11"/>
     </row>
@@ -1330,13 +1342,13 @@
         <v>44</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>34</v>
@@ -1351,13 +1363,13 @@
         <v>45</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>34</v>
@@ -1372,13 +1384,13 @@
         <v>42</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>35</v>
@@ -1393,20 +1405,20 @@
         <v>43</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -1550,7 +1562,7 @@
       <c r="J12" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1578,13 +1590,13 @@
         <v>8</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
         <v>30</v>
@@ -1729,7 +1741,7 @@
       <c r="G12" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1748,7 +1760,7 @@
     <col min="7" max="7" width="15.25" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.25" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
@@ -1758,7 +1770,7 @@
         <v>59</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1787,16 +1799,16 @@
         <v>57</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1823,13 +1835,13 @@
         <v>63</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -1849,10 +1861,13 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I4" s="2">
         <v>500</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1</v>
       </c>
       <c r="K4" s="2">
         <v>1</v>
@@ -1875,13 +1890,13 @@
         <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I5" s="2">
         <v>500</v>
       </c>
       <c r="J5" s="2">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="K5" s="2">
         <v>2</v>
@@ -1897,7 +1912,7 @@
       <c r="H10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -1924,7 +1939,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1940,28 +1955,28 @@
         <v>2</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I2" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="J2" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -1985,7 +2000,7 @@
         <v>46</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>41</v>
@@ -2008,7 +2023,7 @@
         <v>30101</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -2078,7 +2093,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="116">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="10" type="noConversion"/>
@@ -106,10 +106,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>Exp</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>!int</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -203,10 +199,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>Sound_ExpDungeon</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>Sound_Town</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -229,22 +221,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>경험치 던전 - 숲</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>경험치 던전 - 동굴</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드던전 - 광산</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드던전 - 마을</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>!int</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -266,22 +242,6 @@
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드 던전</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>경험치 던전</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>대량의 경험치 획득 가능</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>대량의 골드 획득 가능</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
@@ -416,10 +376,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>Icon_ExpDungeon</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>MapPrefab_Field_1-2</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -428,15 +384,129 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>MapPrefab_GoldDungeon_2</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_ExpDungeon_1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_ExpDungeon_2</t>
+    <t>Dungeon</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>2001;2002;2003</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonStage</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonType</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapID</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterLevel</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardExp</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardGroupID</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>TimeLimit</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxRevivalCount</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>RevivalCostType</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>RevivalCost</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>RevivalCostRatioStep</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rift</t>
+  </si>
+  <si>
+    <t>Rift</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>고브의 금고</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>심연의 균열</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>망자의 미궁</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>고대의 유적</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>끊임없는 연속 스폰
+적의 수가 20%이하가 되면 바로 스폰한다.
+(경험치 획득)</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>웨이브형
+소환됨 몬스터를 다 죽이면 다음 웨이브가 시작됨
+(재화보상)</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>탈출형 기믹
+왼쪽에서 즉사기가 다가오고 상자획득 및 몬스터 전투 후 탈출
+(고급상자 전리품 획득)</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>샌드백
+유적이 등장하고 내가 부순다 페이스마다 함정 발동
+(유물획득)</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_RiftDungeon</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapPrefab_RiftDungeon_1</t>
+  </si>
+  <si>
+    <t>Sound_RiftDungeon</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
@@ -444,67 +514,27 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>Dungeon</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>2001;2002;2003</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>DungeonStage</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>DungeonType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stage</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>MonsterLevel</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>RewardExp</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>RewardGroupID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>TimeLimit</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxRevivalCount</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>RevivalCostType</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>RevivalCost</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>RevivalCostRatioStep</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
+    <t>Labyrinth</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ruins</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드 던전</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>균열 던전</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>미궁던전</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>유적던전</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -710,7 +740,7 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -758,6 +788,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1057,23 +1090,23 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1108,7 +1141,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1131,10 +1164,10 @@
         <v>12</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>4</v>
@@ -1160,7 +1193,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>11</v>
@@ -1178,23 +1211,23 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="2">
-        <v>10001</v>
+        <v>1</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="10" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -1205,23 +1238,23 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
-        <v>20101</v>
+        <v>1001</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="I5"/>
       <c r="L5"/>
@@ -1230,23 +1263,23 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
-        <v>20102</v>
+        <v>1002</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="I6"/>
       <c r="L6"/>
@@ -1255,166 +1288,143 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
-        <v>20103</v>
+        <v>1003</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
-        <v>20201</v>
+        <v>1004</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
-        <v>20202</v>
+        <v>1005</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
-        <v>20203</v>
+        <v>1006</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="K10" s="11"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
-        <v>30101</v>
+        <v>2001</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
-        <v>30102</v>
+        <v>3001</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="K12" s="11"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
-        <v>30201</v>
+        <v>4001</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K13" s="11"/>
+        <v>114</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
-        <v>30202</v>
+        <v>5001</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1449,7 +1459,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1472,7 +1482,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
@@ -1495,7 +1505,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
@@ -1510,11 +1520,11 @@
         <v>1</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1531,11 +1541,11 @@
         <v>2</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -1590,25 +1600,25 @@
         <v>8</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>31</v>
-      </c>
-      <c r="F2" t="s">
-        <v>32</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
@@ -1620,16 +1630,16 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
@@ -1754,7 +1764,7 @@
     <col min="1" max="1" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.75" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.25" style="2" bestFit="1" customWidth="1"/>
@@ -1767,10 +1777,10 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1784,104 +1794,87 @@
         <v>2</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="2">
-        <v>5</v>
-      </c>
-      <c r="G4" s="2">
-        <v>30</v>
-      </c>
-      <c r="H4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I4" s="2">
-        <v>500</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="H4"/>
+    </row>
+    <row r="5" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>54</v>
+        <v>98</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>101</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
@@ -1890,20 +1883,57 @@
         <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I5" s="2">
         <v>500</v>
       </c>
       <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2">
+        <v>30</v>
+      </c>
+      <c r="H6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="2">
+        <v>500</v>
+      </c>
+      <c r="J6" s="2">
         <v>2</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K6" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H8"/>
+    <row r="7" spans="1:11" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H9"/>
@@ -1939,7 +1969,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1955,28 +1985,28 @@
         <v>2</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -1985,25 +2015,25 @@
         <v>6</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>10</v>
@@ -2020,10 +2050,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="2">
-        <v>30101</v>
+        <v>2001</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -2043,7 +2073,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="2">
-        <v>30102</v>
+        <v>2002</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="G5" s="2">
         <v>50</v>
@@ -2057,13 +2090,16 @@
         <v>20001</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
       <c r="E6" s="2">
-        <v>30201</v>
+        <v>3001</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -2077,13 +2113,16 @@
         <v>20002</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D7" s="2">
         <v>2</v>
       </c>
       <c r="E7" s="2">
-        <v>30202</v>
+        <v>3002</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="G7" s="2">
         <v>50</v>
